--- a/Computed_Flux/all_fluxes.xlsx
+++ b/Computed_Flux/all_fluxes.xlsx
@@ -473,37 +473,37 @@
         <v>12</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>45826</v>
+        <v>45810</v>
       </c>
       <c r="C2" t="n">
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0161428369184392</v>
+        <v>0.00852615659395745</v>
       </c>
       <c r="E2" t="n">
-        <v>0.999949024080362</v>
+        <v>0.938475684944881</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45826</v>
+        <v>45810</v>
       </c>
       <c r="G2" t="n">
-        <v>22.4727368932343</v>
+        <v>11.5436877936052</v>
       </c>
       <c r="H2" t="n">
-        <v>31.3</v>
+        <v>30</v>
       </c>
       <c r="I2" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0000103723728378844</v>
+        <v>0.00000550187714442813</v>
       </c>
       <c r="K2" t="n">
-        <v>2946.55068196641</v>
+        <v>802.851623827836</v>
       </c>
       <c r="L2" t="n">
-        <v>2946.55068196641</v>
+        <v>802.851623827836</v>
       </c>
     </row>
     <row r="3">
@@ -511,37 +511,37 @@
         <v>12</v>
       </c>
       <c r="B3" s="1" t="n">
-        <v>45835</v>
+        <v>45817</v>
       </c>
       <c r="C3" t="n">
         <v>120</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00406004253624169</v>
+        <v>0.0384171209077516</v>
       </c>
       <c r="E3" t="n">
-        <v>0.99994162461999</v>
+        <v>0.9833846502304</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45835</v>
+        <v>45817</v>
       </c>
       <c r="G3" t="n">
-        <v>21.4816724032742</v>
+        <v>11.8683468506611</v>
       </c>
       <c r="H3" t="n">
-        <v>28.8</v>
+        <v>31</v>
       </c>
       <c r="I3" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00000263033800731868</v>
+        <v>0.00002470878799157</v>
       </c>
       <c r="K3" t="n">
-        <v>714.265179635261</v>
+        <v>3706.9907488991</v>
       </c>
       <c r="L3" t="n">
-        <v>714.265179635261</v>
+        <v>3706.9907488991</v>
       </c>
     </row>
     <row r="4">
@@ -549,37 +549,37 @@
         <v>12</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>45842</v>
+        <v>45826</v>
       </c>
       <c r="C4" t="n">
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00265153031703296</v>
+        <v>0.0161428369184558</v>
       </c>
       <c r="E4" t="n">
-        <v>0.999967781420424</v>
+        <v>0.999949024080334</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45842</v>
+        <v>45826</v>
       </c>
       <c r="G4" t="n">
-        <v>31.6930541136218</v>
+        <v>22.4727368932343</v>
       </c>
       <c r="H4" t="n">
-        <v>25</v>
+        <v>31.3</v>
       </c>
       <c r="I4" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00000173972476318187</v>
+        <v>0.000010372372837895</v>
       </c>
       <c r="K4" t="n">
-        <v>696.986660935336</v>
+        <v>2946.55068196944</v>
       </c>
       <c r="L4" t="n">
-        <v>696.986660935336</v>
+        <v>2946.55068196944</v>
       </c>
     </row>
     <row r="5">
@@ -587,650 +587,650 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>45849</v>
+        <v>45835</v>
       </c>
       <c r="C5" t="n">
         <v>120</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00343382642595854</v>
+        <v>0.00406004253624169</v>
       </c>
       <c r="E5" t="n">
-        <v>0.999936331346772</v>
+        <v>0.99994162461999</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45849</v>
+        <v>45835</v>
       </c>
       <c r="G5" t="n">
-        <v>41.7677372736301</v>
+        <v>21.4816724032742</v>
       </c>
       <c r="H5" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="I5" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00000222537518304034</v>
+        <v>0.00000263033800731868</v>
       </c>
       <c r="K5" t="n">
-        <v>1174.9625330743</v>
+        <v>714.265179635261</v>
       </c>
       <c r="L5" t="n">
-        <v>1174.9625330743</v>
+        <v>714.265179635261</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="n">
-        <v>45826</v>
+        <v>45842</v>
       </c>
       <c r="C6" t="n">
         <v>120</v>
       </c>
       <c r="D6" t="n">
-        <v>0.032327188896491</v>
+        <v>0.0026515303170357</v>
       </c>
       <c r="E6" t="n">
-        <v>0.999976824230228</v>
+        <v>0.999967781420412</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45826</v>
+        <v>45842</v>
       </c>
       <c r="G6" t="n">
-        <v>22.3018637053101</v>
+        <v>31.6930541136218</v>
       </c>
       <c r="H6" t="n">
-        <v>31.7</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0000207441526164976</v>
+        <v>0.00000173972476318367</v>
       </c>
       <c r="K6" t="n">
-        <v>5848.1255198899</v>
+        <v>696.986660936058</v>
       </c>
       <c r="L6" t="n">
-        <v>5848.1255198899</v>
+        <v>696.986660936058</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>45835</v>
+        <v>45849</v>
       </c>
       <c r="C7" t="n">
         <v>120</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00440630312627471</v>
+        <v>0.00343382642595854</v>
       </c>
       <c r="E7" t="n">
-        <v>0.999989505439658</v>
+        <v>0.999936331346772</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>45835</v>
+        <v>45849</v>
       </c>
       <c r="G7" t="n">
-        <v>22.0968158798011</v>
+        <v>41.7677372736301</v>
       </c>
       <c r="H7" t="n">
-        <v>29.6</v>
+        <v>28.7</v>
       </c>
       <c r="I7" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00000284711925927191</v>
+        <v>0.00000222537518304034</v>
       </c>
       <c r="K7" t="n">
-        <v>795.271071959193</v>
+        <v>1174.9625330743</v>
       </c>
       <c r="L7" t="n">
-        <v>795.271071959193</v>
+        <v>1174.9625330743</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="n">
-        <v>45842</v>
+        <v>45856</v>
       </c>
       <c r="C8" t="n">
         <v>120</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0109745773980604</v>
+        <v>0.00761321598834845</v>
       </c>
       <c r="E8" t="n">
-        <v>0.99997982892961</v>
+        <v>0.999988710371362</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>45842</v>
+        <v>45856</v>
       </c>
       <c r="G8" t="n">
-        <v>31.6930541136218</v>
+        <v>41.2722050286501</v>
       </c>
       <c r="H8" t="n">
-        <v>27.2</v>
+        <v>24.4</v>
       </c>
       <c r="I8" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00000714788126945186</v>
+        <v>0.00000500526872472038</v>
       </c>
       <c r="K8" t="n">
-        <v>2863.65866842391</v>
+        <v>2611.34889449815</v>
       </c>
       <c r="L8" t="n">
-        <v>2863.65866842391</v>
+        <v>2611.34889449815</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="1" t="n">
-        <v>45849</v>
+        <v>45863</v>
       </c>
       <c r="C9" t="n">
         <v>120</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00172416940861672</v>
+        <v>0.00401901721380882</v>
       </c>
       <c r="E9" t="n">
-        <v>0.999628187728139</v>
+        <v>0.999979168341463</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45849</v>
+        <v>45863</v>
       </c>
       <c r="G9" t="n">
-        <v>41.3405543038197</v>
+        <v>41.9044358239695</v>
       </c>
       <c r="H9" t="n">
-        <v>29.3</v>
+        <v>23.9</v>
       </c>
       <c r="I9" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00000111517236920596</v>
+        <v>0.00000264673146817559</v>
       </c>
       <c r="K9" t="n">
-        <v>582.771258652471</v>
+        <v>1402.00546993629</v>
       </c>
       <c r="L9" t="n">
-        <v>582.771258652471</v>
+        <v>1402.00546993629</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>45826</v>
+        <v>45873</v>
       </c>
       <c r="C10" t="n">
         <v>120</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0184261865248611</v>
+        <v>0.00779259859236445</v>
       </c>
       <c r="E10" t="n">
-        <v>0.999922451249564</v>
+        <v>0.999778295714622</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45826</v>
+        <v>45873</v>
       </c>
       <c r="G10" t="n">
-        <v>22.6436100811584</v>
+        <v>42.2120075622329</v>
       </c>
       <c r="H10" t="n">
-        <v>29.9</v>
+        <v>24</v>
       </c>
       <c r="I10" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0000118942319106095</v>
+        <v>0.00000513010280879084</v>
       </c>
       <c r="K10" t="n">
-        <v>3404.5671073418</v>
+        <v>2737.42295658807</v>
       </c>
       <c r="L10" t="n">
-        <v>3404.5671073418</v>
+        <v>2737.42295658807</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="n">
-        <v>45835</v>
+        <v>45810</v>
       </c>
       <c r="C11" t="n">
         <v>120</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0113376057580274</v>
+        <v>0.00961515535090096</v>
       </c>
       <c r="E11" t="n">
-        <v>0.999954598561453</v>
+        <v>0.876255115215493</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>45835</v>
+        <v>45810</v>
       </c>
       <c r="G11" t="n">
-        <v>21.5329343596514</v>
+        <v>11.3215526493038</v>
       </c>
       <c r="H11" t="n">
-        <v>28.8</v>
+        <v>30</v>
       </c>
       <c r="I11" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J11" t="n">
-        <v>0.00000734517805444964</v>
+        <v>0.00000620460143820716</v>
       </c>
       <c r="K11" t="n">
-        <v>1999.33410190424</v>
+        <v>887.972894054391</v>
       </c>
       <c r="L11" t="n">
-        <v>1999.33410190424</v>
+        <v>887.972894054391</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="1" t="n">
-        <v>45842</v>
+        <v>45817</v>
       </c>
       <c r="C12" t="n">
         <v>120</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00197242323194892</v>
+        <v>0.0358141638504435</v>
       </c>
       <c r="E12" t="n">
-        <v>0.999947812608019</v>
+        <v>0.982230962863875</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>45842</v>
+        <v>45817</v>
       </c>
       <c r="G12" t="n">
-        <v>32.3765468653184</v>
+        <v>12.4322283708108</v>
       </c>
       <c r="H12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I12" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J12" t="n">
-        <v>0.00000129414833315447</v>
+        <v>0.000023034640825919</v>
       </c>
       <c r="K12" t="n">
-        <v>529.656630645398</v>
+        <v>3620.01402513419</v>
       </c>
       <c r="L12" t="n">
-        <v>529.656630645398</v>
+        <v>3620.01402513419</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" s="1" t="n">
-        <v>45849</v>
+        <v>45826</v>
       </c>
       <c r="C13" t="n">
         <v>120</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0141142337271372</v>
+        <v>0.0323271888965244</v>
       </c>
       <c r="E13" t="n">
-        <v>0.99983371870182</v>
+        <v>0.999976824230213</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>45849</v>
+        <v>45826</v>
       </c>
       <c r="G13" t="n">
-        <v>41.7677372736301</v>
+        <v>22.3018637053101</v>
       </c>
       <c r="H13" t="n">
-        <v>29.5</v>
+        <v>31.7</v>
       </c>
       <c r="I13" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0000091228836938988</v>
+        <v>0.000020744152616519</v>
       </c>
       <c r="K13" t="n">
-        <v>4816.73679818835</v>
+        <v>5848.12551989594</v>
       </c>
       <c r="L13" t="n">
-        <v>4816.73679818835</v>
+        <v>5848.12551989594</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>45826</v>
+        <v>45835</v>
       </c>
       <c r="C14" t="n">
         <v>120</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0387548748184528</v>
+        <v>0.00440630312627015</v>
       </c>
       <c r="E14" t="n">
-        <v>0.999976134023145</v>
+        <v>0.99998950543967</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>45826</v>
+        <v>45835</v>
       </c>
       <c r="G14" t="n">
-        <v>22.3873002992722</v>
+        <v>22.0968158798011</v>
       </c>
       <c r="H14" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="I14" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0000250330709157015</v>
+        <v>0.00000284711925926897</v>
       </c>
       <c r="K14" t="n">
-        <v>7084.27944063002</v>
+        <v>795.27107195837</v>
       </c>
       <c r="L14" t="n">
-        <v>7084.27944063002</v>
+        <v>795.27107195837</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>45835</v>
+        <v>45842</v>
       </c>
       <c r="C15" t="n">
         <v>120</v>
       </c>
       <c r="D15" t="n">
-        <v>0.00522502802466331</v>
+        <v>0.0109745773980718</v>
       </c>
       <c r="E15" t="n">
-        <v>0.99998968602886</v>
+        <v>0.999979828929599</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>45835</v>
+        <v>45842</v>
       </c>
       <c r="G15" t="n">
-        <v>21.2766245777652</v>
+        <v>31.6930541136218</v>
       </c>
       <c r="H15" t="n">
-        <v>28.4</v>
+        <v>27.2</v>
       </c>
       <c r="I15" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00000338957765779204</v>
+        <v>0.00000714788126945927</v>
       </c>
       <c r="K15" t="n">
-        <v>911.650024821385</v>
+        <v>2863.65866842687</v>
       </c>
       <c r="L15" t="n">
-        <v>911.650024821385</v>
+        <v>2863.65866842687</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="C16" t="n">
         <v>120</v>
       </c>
       <c r="D16" t="n">
-        <v>0.00351532600122298</v>
+        <v>0.00172416940861672</v>
       </c>
       <c r="E16" t="n">
-        <v>0.999967920393618</v>
+        <v>0.999628187728139</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="G16" t="n">
-        <v>31.6930541136218</v>
+        <v>41.3405543038197</v>
       </c>
       <c r="H16" t="n">
-        <v>25.2</v>
+        <v>29.3</v>
       </c>
       <c r="I16" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00000230493232988262</v>
+        <v>0.00000111517236920596</v>
       </c>
       <c r="K16" t="n">
-        <v>923.426005242675</v>
+        <v>582.771258652471</v>
       </c>
       <c r="L16" t="n">
-        <v>923.426005242675</v>
+        <v>582.771258652471</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="C17" t="n">
         <v>120</v>
       </c>
       <c r="D17" t="n">
-        <v>0.00680159312897981</v>
+        <v>0.0109213230673805</v>
       </c>
       <c r="E17" t="n">
-        <v>0.999954148146022</v>
+        <v>0.999987224764265</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="G17" t="n">
-        <v>41.4259908977818</v>
+        <v>41.682300679668</v>
       </c>
       <c r="H17" t="n">
-        <v>30</v>
+        <v>25.1</v>
       </c>
       <c r="I17" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00000438902679884561</v>
+        <v>0.00000716330578332502</v>
       </c>
       <c r="K17" t="n">
-        <v>2298.37541327764</v>
+        <v>3774.37460704209</v>
       </c>
       <c r="L17" t="n">
-        <v>2298.37541327764</v>
+        <v>3774.37460704209</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>45826</v>
+        <v>45863</v>
       </c>
       <c r="C18" t="n">
         <v>120</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0300213622117599</v>
+        <v>0.00276304036107364</v>
       </c>
       <c r="E18" t="n">
-        <v>0.999967267728062</v>
+        <v>0.999965019020879</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>45826</v>
+        <v>45863</v>
       </c>
       <c r="G18" t="n">
-        <v>22.4385622556494</v>
+        <v>42.6562778508357</v>
       </c>
       <c r="H18" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I18" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0000193726029750076</v>
+        <v>0.00000181899284932183</v>
       </c>
       <c r="K18" t="n">
-        <v>5494.93846570893</v>
+        <v>980.83008292323</v>
       </c>
       <c r="L18" t="n">
-        <v>5494.93846570893</v>
+        <v>980.83008292323</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>45835</v>
+        <v>45873</v>
       </c>
       <c r="C19" t="n">
         <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00275590080205934</v>
+        <v>0.0107433521318693</v>
       </c>
       <c r="E19" t="n">
-        <v>0.999905731040506</v>
+        <v>0.999922298721432</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45835</v>
+        <v>45873</v>
       </c>
       <c r="G19" t="n">
-        <v>21.9601173294618</v>
+        <v>42.2120075622329</v>
       </c>
       <c r="H19" t="n">
-        <v>29.9</v>
+        <v>23.8</v>
       </c>
       <c r="I19" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J19" t="n">
-        <v>0.00000177895318806752</v>
+        <v>0.00000707743886014528</v>
       </c>
       <c r="K19" t="n">
-        <v>493.831746277201</v>
+        <v>3776.52151072127</v>
       </c>
       <c r="L19" t="n">
-        <v>493.831746277201</v>
+        <v>3776.52151072127</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>45842</v>
+        <v>45810</v>
       </c>
       <c r="C20" t="n">
         <v>120</v>
       </c>
       <c r="D20" t="n">
-        <v>0.00388208408549379</v>
+        <v>0.0117192507715757</v>
       </c>
       <c r="E20" t="n">
-        <v>0.999982579155091</v>
+        <v>0.980776409101458</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>45842</v>
+        <v>45810</v>
       </c>
       <c r="G20" t="n">
-        <v>32.0860624458474</v>
+        <v>11.6632990251521</v>
       </c>
       <c r="H20" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00000254711695088034</v>
+        <v>0.00000756236145318395</v>
       </c>
       <c r="K20" t="n">
-        <v>1033.10660845663</v>
+        <v>1114.95841751639</v>
       </c>
       <c r="L20" t="n">
-        <v>1033.10660845663</v>
+        <v>1114.95841751639</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>45849</v>
+        <v>45817</v>
       </c>
       <c r="C21" t="n">
         <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>0.00236392645644222</v>
+        <v>0.0405879638667032</v>
       </c>
       <c r="E21" t="n">
-        <v>0.999791776817101</v>
+        <v>0.99258412517036</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>45849</v>
+        <v>45817</v>
       </c>
       <c r="G21" t="n">
-        <v>41.887348505177</v>
+        <v>12.0221327197928</v>
       </c>
       <c r="H21" t="n">
-        <v>29.3</v>
+        <v>31</v>
       </c>
       <c r="I21" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J21" t="n">
-        <v>0.00000152895965668148</v>
+        <v>0.0000261050117888849</v>
       </c>
       <c r="K21" t="n">
-        <v>809.578051527371</v>
+        <v>3967.21046532345</v>
       </c>
       <c r="L21" t="n">
-        <v>809.578051527371</v>
+        <v>3967.21046532345</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B22" s="1" t="n">
         <v>45826</v>
@@ -1239,36 +1239,36 @@
         <v>120</v>
       </c>
       <c r="D22" t="n">
-        <v>0.017186444095651</v>
+        <v>0.0184261865248801</v>
       </c>
       <c r="E22" t="n">
-        <v>0.999975302123136</v>
+        <v>0.999922451249539</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>45826</v>
       </c>
       <c r="G22" t="n">
-        <v>21.9601173294618</v>
+        <v>22.6436100811584</v>
       </c>
       <c r="H22" t="n">
-        <v>29.3</v>
+        <v>29.9</v>
       </c>
       <c r="I22" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0000111159886520371</v>
+        <v>0.0000118942319106217</v>
       </c>
       <c r="K22" t="n">
-        <v>3085.76309059387</v>
+        <v>3404.56710734529</v>
       </c>
       <c r="L22" t="n">
-        <v>3085.76309059387</v>
+        <v>3404.56710734529</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>45835</v>
@@ -1277,36 +1277,36 @@
         <v>120</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0121073716075058</v>
+        <v>0.0113376057580274</v>
       </c>
       <c r="E23" t="n">
-        <v>0.999982616634831</v>
+        <v>0.999954598561453</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="G23" t="n">
-        <v>21.2766245777652</v>
+        <v>21.5329343596514</v>
       </c>
       <c r="H23" t="n">
-        <v>28.2</v>
+        <v>28.8</v>
       </c>
       <c r="I23" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J23" t="n">
-        <v>0.00000785950359527452</v>
+        <v>0.00000734517805444964</v>
       </c>
       <c r="K23" t="n">
-        <v>2113.86708643315</v>
+        <v>1999.33410190424</v>
       </c>
       <c r="L23" t="n">
-        <v>2113.86708643315</v>
+        <v>1999.33410190424</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>45842</v>
@@ -1315,36 +1315,36 @@
         <v>120</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00443971032380894</v>
+        <v>0.00197242323195096</v>
       </c>
       <c r="E24" t="n">
-        <v>0.999948995456845</v>
+        <v>0.999947812607999</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="G24" t="n">
-        <v>31.4367443317356</v>
+        <v>32.3765468653184</v>
       </c>
       <c r="H24" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="I24" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J24" t="n">
-        <v>0.00000291592273709881</v>
+        <v>0.00000129414833315581</v>
       </c>
       <c r="K24" t="n">
-        <v>1158.7597584636</v>
+        <v>529.656630645944</v>
       </c>
       <c r="L24" t="n">
-        <v>1158.7597584636</v>
+        <v>529.656630645944</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>45849</v>
@@ -1353,1252 +1353,1252 @@
         <v>120</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0111717418967619</v>
+        <v>0.0141142337271372</v>
       </c>
       <c r="E25" t="n">
-        <v>0.999940210187543</v>
+        <v>0.99983371870182</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="G25" t="n">
-        <v>41.5456021293287</v>
+        <v>41.7677372736301</v>
       </c>
       <c r="H25" t="n">
-        <v>28.5</v>
+        <v>29.5</v>
       </c>
       <c r="I25" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0000072449232532549</v>
+        <v>0.0000091228836938988</v>
       </c>
       <c r="K25" t="n">
-        <v>3804.85995259262</v>
+        <v>4816.73679818835</v>
       </c>
       <c r="L25" t="n">
-        <v>3804.85995259262</v>
+        <v>4816.73679818835</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>45826</v>
+        <v>45856</v>
       </c>
       <c r="C26" t="n">
         <v>120</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0138921650352256</v>
+        <v>0.00629029750982251</v>
       </c>
       <c r="E26" t="n">
-        <v>0.999970034093763</v>
+        <v>0.999964315043584</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>45826</v>
+        <v>45856</v>
       </c>
       <c r="G26" t="n">
-        <v>21.9601173294618</v>
+        <v>42.1094836494784</v>
       </c>
       <c r="H26" t="n">
-        <v>29.5</v>
+        <v>25.5</v>
       </c>
       <c r="I26" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00000897934725490168</v>
+        <v>0.00000412028316065036</v>
       </c>
       <c r="K26" t="n">
-        <v>2492.63823526153</v>
+        <v>2193.24328610956</v>
       </c>
       <c r="L26" t="n">
-        <v>2492.63823526153</v>
+        <v>2193.24328610956</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>45835</v>
+        <v>45863</v>
       </c>
       <c r="C27" t="n">
         <v>120</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00122601307478599</v>
+        <v>0.0103945396308088</v>
       </c>
       <c r="E27" t="n">
-        <v>0.999901316214843</v>
+        <v>0.99997928380287</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>45835</v>
+        <v>45863</v>
       </c>
       <c r="G27" t="n">
-        <v>20.5931318260685</v>
+        <v>41.9044358239695</v>
       </c>
       <c r="H27" t="n">
-        <v>26.5</v>
+        <v>22.5</v>
       </c>
       <c r="I27" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J27" t="n">
-        <v>0.000000800384163807254</v>
+        <v>0.0000068777753517191</v>
       </c>
       <c r="K27" t="n">
-        <v>208.353459554157</v>
+        <v>3643.24026825053</v>
       </c>
       <c r="L27" t="n">
-        <v>208.353459554157</v>
+        <v>3643.24026825053</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>45842</v>
+        <v>45873</v>
       </c>
       <c r="C28" t="n">
         <v>120</v>
       </c>
       <c r="D28" t="n">
-        <v>0.00246474191640954</v>
+        <v>0.00885833370485613</v>
       </c>
       <c r="E28" t="n">
-        <v>0.999922899771091</v>
+        <v>0.999981602019771</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>45842</v>
+        <v>45873</v>
       </c>
       <c r="G28" t="n">
-        <v>31.3513077377735</v>
+        <v>42.4854046629116</v>
       </c>
       <c r="H28" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="I28" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00000162206783073183</v>
+        <v>0.00000582582372335737</v>
       </c>
       <c r="K28" t="n">
-        <v>642.842381752943</v>
+        <v>3128.79369665423</v>
       </c>
       <c r="L28" t="n">
-        <v>642.842381752943</v>
+        <v>3128.79369665423</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>45849</v>
+        <v>45810</v>
       </c>
       <c r="C29" t="n">
         <v>120</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00217979571467281</v>
+        <v>0.00951539056631892</v>
       </c>
       <c r="E29" t="n">
-        <v>0.999920170634375</v>
+        <v>0.947141127483764</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>45849</v>
+        <v>45810</v>
       </c>
       <c r="G29" t="n">
-        <v>39.6489097433706</v>
+        <v>11.5436877936052</v>
       </c>
       <c r="H29" t="n">
-        <v>28.6</v>
+        <v>30</v>
       </c>
       <c r="I29" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0000014131383075362</v>
+        <v>0.00000614022382772558</v>
       </c>
       <c r="K29" t="n">
-        <v>708.264946681898</v>
+        <v>896.001226735543</v>
       </c>
       <c r="L29" t="n">
-        <v>708.264946681898</v>
+        <v>896.001226735543</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>45826</v>
+        <v>45817</v>
       </c>
       <c r="C30" t="n">
         <v>120</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0185260122320824</v>
+        <v>0.0213836662965812</v>
       </c>
       <c r="E30" t="n">
-        <v>0.999931805148572</v>
+        <v>0.991640613139031</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>45826</v>
+        <v>45817</v>
       </c>
       <c r="G30" t="n">
-        <v>22.3018637053101</v>
+        <v>11.6803863439445</v>
       </c>
       <c r="H30" t="n">
-        <v>29.5</v>
+        <v>31</v>
       </c>
       <c r="I30" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J30" t="n">
-        <v>0.0000119744832183188</v>
+        <v>0.0000137533595574075</v>
       </c>
       <c r="K30" t="n">
-        <v>3375.80821888337</v>
+        <v>2030.70030492232</v>
       </c>
       <c r="L30" t="n">
-        <v>3375.80821888337</v>
+        <v>2030.70030492232</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>45835</v>
+        <v>45826</v>
       </c>
       <c r="C31" t="n">
         <v>120</v>
       </c>
       <c r="D31" t="n">
-        <v>0.00448229419590841</v>
+        <v>0.0387548748184929</v>
       </c>
       <c r="E31" t="n">
-        <v>0.999977022227539</v>
+        <v>0.999976134023132</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>45835</v>
+        <v>45826</v>
       </c>
       <c r="G31" t="n">
-        <v>21.4133231281045</v>
+        <v>22.3873002992722</v>
       </c>
       <c r="H31" t="n">
-        <v>29.9</v>
+        <v>29.7</v>
       </c>
       <c r="I31" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00000289335216409437</v>
+        <v>0.0000250330709157274</v>
       </c>
       <c r="K31" t="n">
-        <v>783.186507035906</v>
+        <v>7084.27944063735</v>
       </c>
       <c r="L31" t="n">
-        <v>783.186507035906</v>
+        <v>7084.27944063735</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>45842</v>
+        <v>45835</v>
       </c>
       <c r="C32" t="n">
         <v>120</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00240401322653006</v>
+        <v>0.0052250280246579</v>
       </c>
       <c r="E32" t="n">
-        <v>0.999958311861582</v>
+        <v>0.999989686028869</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>45842</v>
+        <v>45835</v>
       </c>
       <c r="G32" t="n">
-        <v>31.6930541136218</v>
+        <v>21.2766245777652</v>
       </c>
       <c r="H32" t="n">
-        <v>25</v>
+        <v>28.4</v>
       </c>
       <c r="I32" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J32" t="n">
-        <v>0.00000157732359850634</v>
+        <v>0.00000338957765778853</v>
       </c>
       <c r="K32" t="n">
-        <v>631.92381427436</v>
+        <v>911.65002482044</v>
       </c>
       <c r="L32" t="n">
-        <v>631.92381427436</v>
+        <v>911.65002482044</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>45849</v>
+        <v>45842</v>
       </c>
       <c r="C33" t="n">
         <v>120</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00386869870816962</v>
+        <v>0.00351532600122662</v>
       </c>
       <c r="E33" t="n">
-        <v>0.999883270047805</v>
+        <v>0.999967920393605</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>45849</v>
+        <v>45842</v>
       </c>
       <c r="G33" t="n">
-        <v>41.5626894481211</v>
+        <v>31.6930541136218</v>
       </c>
       <c r="H33" t="n">
-        <v>29.1</v>
+        <v>25.2</v>
       </c>
       <c r="I33" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00000250388509768231</v>
+        <v>0.00000230493232988501</v>
       </c>
       <c r="K33" t="n">
-        <v>1315.52124698387</v>
+        <v>923.42600524363</v>
       </c>
       <c r="L33" t="n">
-        <v>1315.52124698387</v>
+        <v>923.42600524363</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>45826</v>
+        <v>45849</v>
       </c>
       <c r="C34" t="n">
         <v>120</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0378758679819808</v>
+        <v>0.00680159312897981</v>
       </c>
       <c r="E34" t="n">
-        <v>0.999989501601636</v>
+        <v>0.999954148146022</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>45826</v>
+        <v>45849</v>
       </c>
       <c r="G34" t="n">
-        <v>22.6436100811584</v>
+        <v>41.4259908977818</v>
       </c>
       <c r="H34" t="n">
-        <v>31.2</v>
+        <v>30</v>
       </c>
       <c r="I34" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0000243446534469118</v>
+        <v>0.00000438902679884561</v>
       </c>
       <c r="K34" t="n">
-        <v>6968.33616394015</v>
+        <v>2298.37541327764</v>
       </c>
       <c r="L34" t="n">
-        <v>6968.33616394015</v>
+        <v>2298.37541327764</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>45835</v>
+        <v>45856</v>
       </c>
       <c r="C35" t="n">
         <v>120</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00940879433343336</v>
+        <v>0.00730473448380977</v>
       </c>
       <c r="E35" t="n">
-        <v>0.999976174233603</v>
+        <v>0.999970757366525</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>45835</v>
+        <v>45856</v>
       </c>
       <c r="G35" t="n">
-        <v>21.8234187791225</v>
+        <v>41.9727850991391</v>
       </c>
       <c r="H35" t="n">
-        <v>27.7</v>
+        <v>24.3</v>
       </c>
       <c r="I35" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J35" t="n">
-        <v>0.00000611787725739897</v>
+        <v>0.00000480407454341853</v>
       </c>
       <c r="K35" t="n">
-        <v>1687.73157419743</v>
+        <v>2548.92674654963</v>
       </c>
       <c r="L35" t="n">
-        <v>1687.73157419743</v>
+        <v>2548.92674654963</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>45842</v>
+        <v>45863</v>
       </c>
       <c r="C36" t="n">
         <v>120</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00288732692318412</v>
+        <v>0.00653991258030074</v>
       </c>
       <c r="E36" t="n">
-        <v>0.999943625550448</v>
+        <v>0.999986684835094</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>45842</v>
+        <v>45863</v>
       </c>
       <c r="G36" t="n">
-        <v>31.8126653451687</v>
+        <v>41.9556977803467</v>
       </c>
       <c r="H36" t="n">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="I36" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J36" t="n">
-        <v>0.00000189443587176706</v>
+        <v>0.00000430832303266596</v>
       </c>
       <c r="K36" t="n">
-        <v>761.833024240302</v>
+        <v>2284.96228575287</v>
       </c>
       <c r="L36" t="n">
-        <v>761.833024240302</v>
+        <v>2284.96228575287</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>45849</v>
+        <v>45873</v>
       </c>
       <c r="C37" t="n">
         <v>120</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0075307547473242</v>
+        <v>0.00686017809446005</v>
       </c>
       <c r="E37" t="n">
-        <v>0.999952121468506</v>
+        <v>0.999965557557852</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>45849</v>
+        <v>45873</v>
       </c>
       <c r="G37" t="n">
-        <v>41.9898724179315</v>
+        <v>42.1778329246481</v>
       </c>
       <c r="H37" t="n">
-        <v>28.9</v>
+        <v>24.3</v>
       </c>
       <c r="I37" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J37" t="n">
-        <v>0.00000487725658127853</v>
+        <v>0.00000451170497982623</v>
       </c>
       <c r="K37" t="n">
-        <v>2588.80886828618</v>
+        <v>2405.49680671009</v>
       </c>
       <c r="L37" t="n">
-        <v>2588.80886828618</v>
+        <v>2405.49680671009</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>45826</v>
+        <v>45810</v>
       </c>
       <c r="C38" t="n">
         <v>120</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00417659215079258</v>
+        <v>0.00642793914510229</v>
       </c>
       <c r="E38" t="n">
-        <v>0.999953612830018</v>
+        <v>0.879302968792153</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>45826</v>
+        <v>45810</v>
       </c>
       <c r="G38" t="n">
-        <v>22.0455539234239</v>
+        <v>11.5436877936052</v>
       </c>
       <c r="H38" t="n">
-        <v>29.3</v>
+        <v>30</v>
       </c>
       <c r="I38" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J38" t="n">
-        <v>0.00000270137037621098</v>
+        <v>0.00000414791014902039</v>
       </c>
       <c r="K38" t="n">
-        <v>752.809303565149</v>
+        <v>605.276401347038</v>
       </c>
       <c r="L38" t="n">
-        <v>752.809303565149</v>
+        <v>605.276401347038</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>45835</v>
+        <v>45817</v>
       </c>
       <c r="C39" t="n">
         <v>120</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00208335721785558</v>
+        <v>0.0329185138118281</v>
       </c>
       <c r="E39" t="n">
-        <v>0.999970447005895</v>
+        <v>0.994469127768906</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>45835</v>
+        <v>45817</v>
       </c>
       <c r="G39" t="n">
-        <v>21.2766245777652</v>
+        <v>12.1588312701321</v>
       </c>
       <c r="H39" t="n">
-        <v>29.7</v>
+        <v>31</v>
       </c>
       <c r="I39" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J39" t="n">
-        <v>0.0000013457101647632</v>
+        <v>0.0000211722419472072</v>
       </c>
       <c r="K39" t="n">
-        <v>361.937925301262</v>
+        <v>3254.15705318998</v>
       </c>
       <c r="L39" t="n">
-        <v>361.937925301262</v>
+        <v>3254.15705318998</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>45842</v>
+        <v>45826</v>
       </c>
       <c r="C40" t="n">
         <v>120</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00104293225579297</v>
+        <v>0.0300213622117909</v>
       </c>
       <c r="E40" t="n">
-        <v>0.999841882724093</v>
+        <v>0.999967267728047</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>45842</v>
+        <v>45826</v>
       </c>
       <c r="G40" t="n">
-        <v>31.6930541136218</v>
+        <v>22.4385622556494</v>
       </c>
       <c r="H40" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I40" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J40" t="n">
-        <v>0.000000684289770352116</v>
+        <v>0.0000193726029750276</v>
       </c>
       <c r="K40" t="n">
-        <v>274.147297459645</v>
+        <v>5494.93846571461</v>
       </c>
       <c r="L40" t="n">
-        <v>274.147297459645</v>
+        <v>5494.93846571461</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>45849</v>
+        <v>45835</v>
       </c>
       <c r="C41" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00213768163937871</v>
+        <v>0.00275590080205934</v>
       </c>
       <c r="E41" t="n">
-        <v>0.999552921215175</v>
+        <v>0.999905731040506</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>45849</v>
+        <v>45835</v>
       </c>
       <c r="G41" t="n">
-        <v>41.5626894481211</v>
+        <v>21.9601173294618</v>
       </c>
       <c r="H41" t="n">
-        <v>28.9</v>
+        <v>29.9</v>
       </c>
       <c r="I41" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J41" t="n">
-        <v>0.00000138445908732357</v>
+        <v>0.00000177895318806752</v>
       </c>
       <c r="K41" t="n">
-        <v>727.38375520502</v>
+        <v>493.831746277201</v>
       </c>
       <c r="L41" t="n">
-        <v>727.38375520502</v>
+        <v>493.831746277201</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>45826</v>
+        <v>45842</v>
       </c>
       <c r="C42" t="n">
         <v>120</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00795094064083457</v>
+        <v>0.00388208408549781</v>
       </c>
       <c r="E42" t="n">
-        <v>0.999961587924764</v>
+        <v>0.999982579155083</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>45826</v>
+        <v>45842</v>
       </c>
       <c r="G42" t="n">
-        <v>21.6183709536135</v>
+        <v>32.0860624458474</v>
       </c>
       <c r="H42" t="n">
-        <v>29.7</v>
+        <v>25</v>
       </c>
       <c r="I42" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J42" t="n">
-        <v>0.00000513577870760598</v>
+        <v>0.00000254711695088299</v>
       </c>
       <c r="K42" t="n">
-        <v>1403.4892686482</v>
+        <v>1033.1066084577</v>
       </c>
       <c r="L42" t="n">
-        <v>1403.4892686482</v>
+        <v>1033.1066084577</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>45835</v>
+        <v>45849</v>
       </c>
       <c r="C43" t="n">
         <v>120</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0025609573709551</v>
+        <v>0.00236392645644222</v>
       </c>
       <c r="E43" t="n">
-        <v>0.999970198004442</v>
+        <v>0.999791776817101</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>45835</v>
+        <v>45849</v>
       </c>
       <c r="G43" t="n">
-        <v>20.0292503059188</v>
+        <v>41.887348505177</v>
       </c>
       <c r="H43" t="n">
-        <v>26.3</v>
+        <v>29.3</v>
       </c>
       <c r="I43" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J43" t="n">
-        <v>0.00000167299962932997</v>
+        <v>0.00000152895965668148</v>
       </c>
       <c r="K43" t="n">
-        <v>423.58480045011</v>
+        <v>809.578051527371</v>
       </c>
       <c r="L43" t="n">
-        <v>423.58480045011</v>
+        <v>809.578051527371</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>45842</v>
+        <v>45856</v>
       </c>
       <c r="C44" t="n">
         <v>120</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00264661829020731</v>
+        <v>0.00769709961184123</v>
       </c>
       <c r="E44" t="n">
-        <v>0.999943998510322</v>
+        <v>0.999992667157638</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>45842</v>
+        <v>45856</v>
       </c>
       <c r="G44" t="n">
-        <v>31.5221809256976</v>
+        <v>42.1094836494784</v>
       </c>
       <c r="H44" t="n">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="I44" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J44" t="n">
-        <v>0.00000173650187915482</v>
+        <v>0.00000507064752552011</v>
       </c>
       <c r="K44" t="n">
-        <v>691.944631498</v>
+        <v>2699.12605710809</v>
       </c>
       <c r="L44" t="n">
-        <v>691.944631498</v>
+        <v>2699.12605710809</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>45849</v>
+        <v>45863</v>
       </c>
       <c r="C45" t="n">
         <v>120</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00450907969787291</v>
+        <v>0.00345919371833085</v>
       </c>
       <c r="E45" t="n">
-        <v>0.999482089700575</v>
+        <v>0.999967816007348</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>45849</v>
+        <v>45863</v>
       </c>
       <c r="G45" t="n">
-        <v>41.2209430722728</v>
+        <v>42.1094836494784</v>
       </c>
       <c r="H45" t="n">
-        <v>29.2</v>
+        <v>22.2</v>
       </c>
       <c r="I45" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J45" t="n">
-        <v>0.00000291738444958433</v>
+        <v>0.00000229117753652618</v>
       </c>
       <c r="K45" t="n">
-        <v>1520.16740554049</v>
+        <v>1219.60301108964</v>
       </c>
       <c r="L45" t="n">
-        <v>1520.16740554049</v>
+        <v>1219.60301108964</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>45826</v>
+        <v>45873</v>
       </c>
       <c r="C46" t="n">
         <v>120</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0163086735388159</v>
+        <v>0.00974218565510042</v>
       </c>
       <c r="E46" t="n">
-        <v>0.999960460481606</v>
+        <v>0.999930580384865</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>45826</v>
+        <v>45873</v>
       </c>
       <c r="G46" t="n">
-        <v>22.6436100811584</v>
+        <v>42.3487061125723</v>
       </c>
       <c r="H46" t="n">
-        <v>29.1</v>
+        <v>24.3</v>
       </c>
       <c r="I46" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J46" t="n">
-        <v>0.0000105552403319945</v>
+        <v>0.00000640710298323061</v>
       </c>
       <c r="K46" t="n">
-        <v>3021.29841712112</v>
+        <v>3429.90174797312</v>
       </c>
       <c r="L46" t="n">
-        <v>3021.29841712112</v>
+        <v>3429.90174797312</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>45835</v>
+        <v>45810</v>
       </c>
       <c r="C47" t="n">
         <v>120</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0053516543347757</v>
+        <v>0.00928795166982792</v>
       </c>
       <c r="E47" t="n">
-        <v>0.999984805551553</v>
+        <v>0.853180626580615</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>45835</v>
+        <v>45810</v>
       </c>
       <c r="G47" t="n">
-        <v>21.8234187791225</v>
+        <v>10.9456316358706</v>
       </c>
       <c r="H47" t="n">
-        <v>28.6</v>
+        <v>30</v>
       </c>
       <c r="I47" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J47" t="n">
-        <v>0.00000346942041323303</v>
+        <v>0.00000599345888709048</v>
       </c>
       <c r="K47" t="n">
-        <v>957.104912246628</v>
+        <v>829.274264965441</v>
       </c>
       <c r="L47" t="n">
-        <v>957.104912246628</v>
+        <v>829.274264965441</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>45842</v>
+        <v>45817</v>
       </c>
       <c r="C48" t="n">
         <v>120</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00622855374882097</v>
+        <v>0.0215472718283504</v>
       </c>
       <c r="E48" t="n">
-        <v>0.999973682107522</v>
+        <v>0.972439324913754</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>45842</v>
+        <v>45817</v>
       </c>
       <c r="G48" t="n">
-        <v>31.9322765767156</v>
+        <v>11.6120370687748</v>
       </c>
       <c r="H48" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I48" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J48" t="n">
-        <v>0.00000408668500828551</v>
+        <v>0.0000138585859331279</v>
       </c>
       <c r="K48" t="n">
-        <v>1649.60846293059</v>
+        <v>2034.26328932924</v>
       </c>
       <c r="L48" t="n">
-        <v>1649.60846293059</v>
+        <v>2034.26328932924</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>45849</v>
+        <v>45826</v>
       </c>
       <c r="C49" t="n">
         <v>120</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00447908471684053</v>
+        <v>0.0171864440956688</v>
       </c>
       <c r="E49" t="n">
-        <v>0.999906874256435</v>
+        <v>0.999975302123121</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>45849</v>
+        <v>45826</v>
       </c>
       <c r="G49" t="n">
-        <v>41.9044358239695</v>
+        <v>21.9601173294618</v>
       </c>
       <c r="H49" t="n">
-        <v>28.3</v>
+        <v>29.3</v>
       </c>
       <c r="I49" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J49" t="n">
-        <v>0.00000290663405283213</v>
+        <v>0.0000111159886520486</v>
       </c>
       <c r="K49" t="n">
-        <v>1539.67899281552</v>
+        <v>3085.76309059706</v>
       </c>
       <c r="L49" t="n">
-        <v>1539.67899281552</v>
+        <v>3085.76309059706</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>45826</v>
+        <v>45835</v>
       </c>
       <c r="C50" t="n">
         <v>120</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0208697229338843</v>
+        <v>0.0121073716075058</v>
       </c>
       <c r="E50" t="n">
-        <v>0.999949076541266</v>
+        <v>0.999982616634831</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>45826</v>
+        <v>45835</v>
       </c>
       <c r="G50" t="n">
-        <v>22.6436100811584</v>
+        <v>21.2766245777652</v>
       </c>
       <c r="H50" t="n">
-        <v>29.7</v>
+        <v>28.2</v>
       </c>
       <c r="I50" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0000134804526305996</v>
+        <v>0.00000785950359527452</v>
       </c>
       <c r="K50" t="n">
-        <v>3858.60188057042</v>
+        <v>2113.86708643315</v>
       </c>
       <c r="L50" t="n">
-        <v>3858.60188057042</v>
+        <v>2113.86708643315</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>45835</v>
+        <v>45842</v>
       </c>
       <c r="C51" t="n">
         <v>120</v>
       </c>
       <c r="D51" t="n">
-        <v>0.000425599785259446</v>
+        <v>0.00443971032381352</v>
       </c>
       <c r="E51" t="n">
-        <v>0.999570378251626</v>
+        <v>0.999948995456825</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>45835</v>
+        <v>45842</v>
       </c>
       <c r="G51" t="n">
-        <v>21.8234187791225</v>
+        <v>31.4367443317356</v>
       </c>
       <c r="H51" t="n">
-        <v>29.5</v>
+        <v>24.7</v>
       </c>
       <c r="I51" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J51" t="n">
-        <v>0.000000275090905828279</v>
+        <v>0.00000291592273710181</v>
       </c>
       <c r="K51" t="n">
-        <v>75.8890033270052</v>
+        <v>1158.7597584648</v>
       </c>
       <c r="L51" t="n">
-        <v>75.8890033270052</v>
+        <v>1158.7597584648</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="C52" t="n">
         <v>120</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0059926698238783</v>
+        <v>0.0111717418967619</v>
       </c>
       <c r="E52" t="n">
-        <v>0.99996948072287</v>
+        <v>0.999940210187543</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="G52" t="n">
-        <v>32.2398483149791</v>
+        <v>41.5456021293287</v>
       </c>
       <c r="H52" t="n">
-        <v>24</v>
+        <v>28.5</v>
       </c>
       <c r="I52" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J52" t="n">
-        <v>0.00000394515538446412</v>
+        <v>0.0000072449232532549</v>
       </c>
       <c r="K52" t="n">
-        <v>1607.81816898095</v>
+        <v>3804.85995259262</v>
       </c>
       <c r="L52" t="n">
-        <v>1607.81816898095</v>
+        <v>3804.85995259262</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="C53" t="n">
         <v>120</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00190458998103238</v>
+        <v>0.00549838247391952</v>
       </c>
       <c r="E53" t="n">
-        <v>0.999808839282718</v>
+        <v>0.999971231350573</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="G53" t="n">
-        <v>41.8531738675922</v>
+        <v>41.4259908977818</v>
       </c>
       <c r="H53" t="n">
-        <v>29.5</v>
+        <v>24.9</v>
       </c>
       <c r="I53" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J53" t="n">
-        <v>0.00000123105180326694</v>
+        <v>0.00000360881530204614</v>
       </c>
       <c r="K53" t="n">
-        <v>651.305214716471</v>
+        <v>1889.8067251411</v>
       </c>
       <c r="L53" t="n">
-        <v>651.305214716471</v>
+        <v>1889.8067251411</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>45826</v>
+        <v>45863</v>
       </c>
       <c r="C54" t="n">
         <v>120</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0155541222754369</v>
+        <v>0.0116197745238253</v>
       </c>
       <c r="E54" t="n">
-        <v>0.999988719531109</v>
+        <v>0.999955557269035</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>45826</v>
+        <v>45863</v>
       </c>
       <c r="G54" t="n">
-        <v>22.6436100811584</v>
+        <v>41.9727850991391</v>
       </c>
       <c r="H54" t="n">
-        <v>31.5</v>
+        <v>23.8</v>
       </c>
       <c r="I54" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J54" t="n">
-        <v>0.00000998753752353095</v>
+        <v>0.00000765480296574237</v>
       </c>
       <c r="K54" t="n">
-        <v>2858.80097105094</v>
+        <v>4061.45488430826</v>
       </c>
       <c r="L54" t="n">
-        <v>2858.80097105094</v>
+        <v>4061.45488430826</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>45835</v>
+        <v>45873</v>
       </c>
       <c r="C55" t="n">
         <v>120</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00433339029264327</v>
+        <v>0.00807096134131474</v>
       </c>
       <c r="E55" t="n">
-        <v>0.999974757447347</v>
+        <v>0.999920908392807</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>45835</v>
+        <v>45873</v>
       </c>
       <c r="G55" t="n">
-        <v>21.4816724032742</v>
+        <v>41.801911911215</v>
       </c>
       <c r="H55" t="n">
-        <v>28.5</v>
+        <v>23.9</v>
       </c>
       <c r="I55" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J55" t="n">
-        <v>0.00000281022246904038</v>
+        <v>0.00000531514701830349</v>
       </c>
       <c r="K55" t="n">
-        <v>763.112592784348</v>
+        <v>2808.60882816944</v>
       </c>
       <c r="L55" t="n">
-        <v>763.112592784348</v>
+        <v>2808.60882816944</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>45842</v>
+        <v>45810</v>
       </c>
       <c r="C56" t="n">
         <v>120</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00253876915526613</v>
+        <v>0.0103902863257011</v>
       </c>
       <c r="E56" t="n">
-        <v>0.999940479434059</v>
+        <v>0.939324529395542</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>45842</v>
+        <v>45810</v>
       </c>
       <c r="G56" t="n">
-        <v>32.0348004894701</v>
+        <v>10.9285443170782</v>
       </c>
       <c r="H56" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I56" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J56" t="n">
-        <v>0.00000166573979525949</v>
+        <v>0.00000670478875557519</v>
       </c>
       <c r="K56" t="n">
-        <v>674.542028147431</v>
+        <v>926.247921016511</v>
       </c>
       <c r="L56" t="n">
-        <v>674.542028147431</v>
+        <v>926.247921016511</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>45849</v>
+        <v>45817</v>
       </c>
       <c r="C57" t="n">
         <v>120</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00511119739466197</v>
+        <v>0.0112009813819314</v>
       </c>
       <c r="E57" t="n">
-        <v>0.999993211124916</v>
+        <v>0.975914197441886</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>45849</v>
+        <v>45817</v>
       </c>
       <c r="G57" t="n">
-        <v>41.6310387232908</v>
+        <v>11.1335921425872</v>
       </c>
       <c r="H57" t="n">
-        <v>28.5</v>
+        <v>31</v>
       </c>
       <c r="I57" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0000033146337606757</v>
+        <v>0.00000720414928875685</v>
       </c>
       <c r="K57" t="n">
-        <v>1744.34596755931</v>
+        <v>1013.90634494399</v>
       </c>
       <c r="L57" t="n">
-        <v>1744.34596755931</v>
+        <v>1013.90634494399</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B58" s="1" t="n">
         <v>45826</v>
@@ -2607,10 +2607,10 @@
         <v>120</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00673608323533396</v>
+        <v>0.0138921650352399</v>
       </c>
       <c r="E58" t="n">
-        <v>0.999917104483587</v>
+        <v>0.999970034093748</v>
       </c>
       <c r="F58" s="1" t="n">
         <v>45826</v>
@@ -2619,24 +2619,24 @@
         <v>21.9601173294618</v>
       </c>
       <c r="H58" t="n">
-        <v>30.2</v>
+        <v>29.5</v>
       </c>
       <c r="I58" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J58" t="n">
-        <v>0.00000434388640999551</v>
+        <v>0.00000897934725491097</v>
       </c>
       <c r="K58" t="n">
-        <v>1205.84904980449</v>
+        <v>2492.6382352641</v>
       </c>
       <c r="L58" t="n">
-        <v>1205.84904980449</v>
+        <v>2492.6382352641</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B59" s="1" t="n">
         <v>45835</v>
@@ -2645,36 +2645,36 @@
         <v>120</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00223921972700177</v>
+        <v>0.00122601307478662</v>
       </c>
       <c r="E59" t="n">
-        <v>0.99990077975205</v>
+        <v>0.999901316214835</v>
       </c>
       <c r="F59" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="G59" t="n">
-        <v>21.4133231281045</v>
+        <v>20.5931318260685</v>
       </c>
       <c r="H59" t="n">
-        <v>27.4</v>
+        <v>26.5</v>
       </c>
       <c r="I59" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J59" t="n">
-        <v>0.00000145746117794117</v>
+        <v>0.000000800384163807667</v>
       </c>
       <c r="K59" t="n">
-        <v>394.51261524864</v>
+        <v>208.353459554264</v>
       </c>
       <c r="L59" t="n">
-        <v>394.51261524864</v>
+        <v>208.353459554264</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B60" s="1" t="n">
         <v>45842</v>
@@ -2683,10 +2683,10 @@
         <v>120</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00114137956916524</v>
+        <v>0.00246474191641209</v>
       </c>
       <c r="E60" t="n">
-        <v>0.999819583231275</v>
+        <v>0.999922899771074</v>
       </c>
       <c r="F60" s="1" t="n">
         <v>45842</v>
@@ -2695,24 +2695,24 @@
         <v>31.3513077377735</v>
       </c>
       <c r="H60" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="I60" t="n">
         <v>0.00000683492751696629</v>
       </c>
       <c r="J60" t="n">
-        <v>0.000000748883121535866</v>
+        <v>0.00000162206783073351</v>
       </c>
       <c r="K60" t="n">
-        <v>296.790183728318</v>
+        <v>642.842381753608</v>
       </c>
       <c r="L60" t="n">
-        <v>296.790183728318</v>
+        <v>642.842381753608</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B61" s="1" t="n">
         <v>45849</v>
@@ -2721,31 +2721,2881 @@
         <v>120</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00303728508128978</v>
+        <v>0.00217979571467281</v>
       </c>
       <c r="E61" t="n">
-        <v>0.999716967865183</v>
+        <v>0.999920170634375</v>
       </c>
       <c r="F61" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="G61" t="n">
+        <v>39.6489097433706</v>
+      </c>
+      <c r="H61" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.0000014131383075362</v>
+      </c>
+      <c r="K61" t="n">
+        <v>708.264946681898</v>
+      </c>
+      <c r="L61" t="n">
+        <v>708.264946681898</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C62" t="n">
+        <v>120</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.00377199057106083</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.999954130113165</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G62" t="n">
         <v>41.4259908977818</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H62" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.00000247820873711528</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1297.74874736552</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1297.74874736552</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C63" t="n">
+        <v>120</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.00371111806057623</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.999962173940636</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G63" t="n">
+        <v>41.3747289414046</v>
+      </c>
+      <c r="H63" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.00000245305233137588</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1282.98566492001</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1282.98566492001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>18</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C64" t="n">
+        <v>120</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.00875141620718942</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.999930057317656</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G64" t="n">
+        <v>41.801911911215</v>
+      </c>
+      <c r="H64" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.00000575163848557317</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3039.25791166093</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3039.25791166093</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C65" t="n">
+        <v>120</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.00888377913494108</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.989459804557794</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G65" t="n">
+        <v>11.3215526493038</v>
+      </c>
+      <c r="H65" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.00000573264880137431</v>
+      </c>
+      <c r="K65" t="n">
+        <v>820.429289044661</v>
+      </c>
+      <c r="L65" t="n">
+        <v>820.429289044661</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C66" t="n">
+        <v>120</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0.0461985232353579</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.984450847833942</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G66" t="n">
+        <v>11.8170848942838</v>
+      </c>
+      <c r="H66" t="n">
+        <v>31</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.0000297135623173612</v>
+      </c>
+      <c r="K66" t="n">
+        <v>4438.5887346754</v>
+      </c>
+      <c r="L66" t="n">
+        <v>4438.5887346754</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>19</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C67" t="n">
+        <v>120</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0.0185260122321014</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.999931805148548</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G67" t="n">
+        <v>22.3018637053101</v>
+      </c>
+      <c r="H67" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.0000119744832183311</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3375.80821888685</v>
+      </c>
+      <c r="L67" t="n">
+        <v>3375.80821888685</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>19</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C68" t="n">
+        <v>120</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0.00448229419590841</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.999977022227539</v>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G68" t="n">
+        <v>21.4133231281045</v>
+      </c>
+      <c r="H68" t="n">
+        <v>29.9</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.00000289335216409437</v>
+      </c>
+      <c r="K68" t="n">
+        <v>783.186507035906</v>
+      </c>
+      <c r="L68" t="n">
+        <v>783.186507035906</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>19</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C69" t="n">
+        <v>120</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.00240401322653255</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.999958311861569</v>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G69" t="n">
+        <v>31.6930541136218</v>
+      </c>
+      <c r="H69" t="n">
+        <v>25</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.00000157732359850797</v>
+      </c>
+      <c r="K69" t="n">
+        <v>631.923814275014</v>
+      </c>
+      <c r="L69" t="n">
+        <v>631.923814275014</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C70" t="n">
+        <v>120</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0.00386869870816962</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.999883270047805</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G70" t="n">
+        <v>41.5626894481211</v>
+      </c>
+      <c r="H70" t="n">
         <v>29.1</v>
       </c>
-      <c r="I61" t="n">
-        <v>0.00000683492751696629</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="I70" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.00000250388509768231</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1315.52124698387</v>
+      </c>
+      <c r="L70" t="n">
+        <v>1315.52124698387</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C71" t="n">
+        <v>120</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0.00636274140089418</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.99997033119691</v>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G71" t="n">
+        <v>41.7677372736301</v>
+      </c>
+      <c r="H71" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.00000418174469694041</v>
+      </c>
+      <c r="K71" t="n">
+        <v>2207.89437180403</v>
+      </c>
+      <c r="L71" t="n">
+        <v>2207.89437180403</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C72" t="n">
+        <v>120</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.00642130932396656</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.999982077600667</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G72" t="n">
+        <v>42.2461821998178</v>
+      </c>
+      <c r="H72" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.00000422876552910431</v>
+      </c>
+      <c r="K72" t="n">
+        <v>2258.29619366983</v>
+      </c>
+      <c r="L72" t="n">
+        <v>2258.29619366983</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>19</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C73" t="n">
+        <v>120</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.0106909489121156</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.999963250450833</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G73" t="n">
+        <v>41.9556977803467</v>
+      </c>
+      <c r="H73" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.00000703107219400199</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3728.99958287456</v>
+      </c>
+      <c r="L73" t="n">
+        <v>3728.99958287456</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C74" t="n">
+        <v>120</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.00796353276724021</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.903300374373784</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G74" t="n">
+        <v>11.5436877936052</v>
+      </c>
+      <c r="H74" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.00000513881940099892</v>
+      </c>
+      <c r="K74" t="n">
+        <v>749.87306919933</v>
+      </c>
+      <c r="L74" t="n">
+        <v>749.87306919933</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>20</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C75" t="n">
+        <v>120</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.0448898963392718</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.995248273875463</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G75" t="n">
+        <v>12.0904819949625</v>
+      </c>
+      <c r="H75" t="n">
+        <v>31</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.0000288718911100602</v>
+      </c>
+      <c r="K75" t="n">
+        <v>4412.64180269369</v>
+      </c>
+      <c r="L75" t="n">
+        <v>4412.64180269369</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>20</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C76" t="n">
+        <v>120</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.03787586798202</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.999989501601628</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G76" t="n">
+        <v>22.6436100811584</v>
+      </c>
+      <c r="H76" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.000024344653446937</v>
+      </c>
+      <c r="K76" t="n">
+        <v>6968.33616394737</v>
+      </c>
+      <c r="L76" t="n">
+        <v>6968.33616394737</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>20</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C77" t="n">
+        <v>120</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.00940879433342363</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.999976174233616</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G77" t="n">
+        <v>21.8234187791225</v>
+      </c>
+      <c r="H77" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.00000611787725739265</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1687.73157419569</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1687.73157419569</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>20</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C78" t="n">
+        <v>120</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.00288732692318114</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.999943625550467</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G78" t="n">
+        <v>31.8126653451687</v>
+      </c>
+      <c r="H78" t="n">
+        <v>25</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.00000189443587176511</v>
+      </c>
+      <c r="K78" t="n">
+        <v>761.833024239517</v>
+      </c>
+      <c r="L78" t="n">
+        <v>761.833024239517</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>20</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C79" t="n">
+        <v>120</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.0075307547473242</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.999952121468506</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G79" t="n">
+        <v>41.9898724179315</v>
+      </c>
+      <c r="H79" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.00000487725658127853</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2588.80886828618</v>
+      </c>
+      <c r="L79" t="n">
+        <v>2588.80886828618</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>20</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C80" t="n">
+        <v>120</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.0102846135401707</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.999963774620079</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G80" t="n">
+        <v>42.1094836494784</v>
+      </c>
+      <c r="H80" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.00000677295190507472</v>
+      </c>
+      <c r="K80" t="n">
+        <v>3605.2695200209</v>
+      </c>
+      <c r="L80" t="n">
+        <v>3605.2695200209</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>20</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C81" t="n">
+        <v>120</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.00695464324210811</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.999974265472618</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G81" t="n">
+        <v>42.4512300253268</v>
+      </c>
+      <c r="H81" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.000004592367780936</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2464.37485564112</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2464.37485564112</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>20</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C82" t="n">
+        <v>120</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.0100865603942972</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.999933325450469</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G82" t="n">
+        <v>42.4512300253268</v>
+      </c>
+      <c r="H82" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.00000664700123001208</v>
+      </c>
+      <c r="K82" t="n">
+        <v>3566.94051479447</v>
+      </c>
+      <c r="L82" t="n">
+        <v>3566.94051479447</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>21</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C83" t="n">
+        <v>120</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.00719700767849887</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.955731186238938</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G83" t="n">
+        <v>11.1506794613796</v>
+      </c>
+      <c r="H83" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.00000464418540971549</v>
+      </c>
+      <c r="K83" t="n">
+        <v>654.622171815671</v>
+      </c>
+      <c r="L83" t="n">
+        <v>654.622171815671</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C84" t="n">
+        <v>120</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.00880647104254166</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.984964303117594</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G84" t="n">
+        <v>11.6803863439445</v>
+      </c>
+      <c r="H84" t="n">
+        <v>31</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.00000566406906094196</v>
+      </c>
+      <c r="K84" t="n">
+        <v>836.306701729539</v>
+      </c>
+      <c r="L84" t="n">
+        <v>836.306701729539</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C85" t="n">
+        <v>120</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.00417659215079688</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.99995361283</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G85" t="n">
+        <v>22.0455539234239</v>
+      </c>
+      <c r="H85" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.00000270137037621376</v>
+      </c>
+      <c r="K85" t="n">
+        <v>752.809303565924</v>
+      </c>
+      <c r="L85" t="n">
+        <v>752.809303565924</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>21</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C86" t="n">
+        <v>120</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.00208335721785666</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.999970447005891</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G86" t="n">
+        <v>21.2766245777652</v>
+      </c>
+      <c r="H86" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.0000013457101647639</v>
+      </c>
+      <c r="K86" t="n">
+        <v>361.937925301449</v>
+      </c>
+      <c r="L86" t="n">
+        <v>361.937925301449</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>21</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C87" t="n">
+        <v>120</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.00104293225579404</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.99984188272407</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G87" t="n">
+        <v>31.6930541136218</v>
+      </c>
+      <c r="H87" t="n">
+        <v>25</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.000000684289770352822</v>
+      </c>
+      <c r="K87" t="n">
+        <v>274.147297459927</v>
+      </c>
+      <c r="L87" t="n">
+        <v>274.147297459927</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C88" t="n">
+        <v>120</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.00187545628708846</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.999893934445622</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G88" t="n">
+        <v>41.5626894481211</v>
+      </c>
+      <c r="H88" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.00000121463011690196</v>
+      </c>
+      <c r="K88" t="n">
+        <v>638.156969539091</v>
+      </c>
+      <c r="L88" t="n">
+        <v>638.156969539091</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>21</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C89" t="n">
+        <v>120</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0.00194156864517003</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.999899346052172</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G89" t="n">
+        <v>41.5626894481211</v>
+      </c>
+      <c r="H89" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.00000127733307243023</v>
+      </c>
+      <c r="K89" t="n">
+        <v>671.100601945576</v>
+      </c>
+      <c r="L89" t="n">
+        <v>671.100601945576</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>21</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C90" t="n">
+        <v>120</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.00322410738112699</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.999949550063213</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G90" t="n">
+        <v>41.9727850991391</v>
+      </c>
+      <c r="H90" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.0000021239574565168</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1126.92089194702</v>
+      </c>
+      <c r="L90" t="n">
+        <v>1126.92089194702</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>21</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C91" t="n">
+        <v>120</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.00546662620243424</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.999956307316251</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G91" t="n">
+        <v>41.9386104615543</v>
+      </c>
+      <c r="H91" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.00000359279651518955</v>
+      </c>
+      <c r="K91" t="n">
+        <v>1904.69958425363</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1904.69958425363</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>22</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C92" t="n">
+        <v>120</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.00816354211963148</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.959419345625445</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G92" t="n">
+        <v>10.7234964915692</v>
+      </c>
+      <c r="H92" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.000005267884223169</v>
+      </c>
+      <c r="K92" t="n">
+        <v>714.089199892923</v>
+      </c>
+      <c r="L92" t="n">
+        <v>714.089199892923</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>22</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C93" t="n">
+        <v>120</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.0142802105155128</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.987619605241375</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G93" t="n">
+        <v>11.4753385184355</v>
+      </c>
+      <c r="H93" t="n">
+        <v>31</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.00000918462096496145</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1332.31394460659</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1332.31394460659</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C94" t="n">
+        <v>120</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.00795094064084278</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.999961587924747</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G94" t="n">
+        <v>21.6183709536135</v>
+      </c>
+      <c r="H94" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.00000513577870761128</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1403.48926864965</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1403.48926864965</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C95" t="n">
+        <v>120</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.00256095737095245</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.999970198004455</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G95" t="n">
+        <v>20.0292503059188</v>
+      </c>
+      <c r="H95" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.00000167299962932824</v>
+      </c>
+      <c r="K95" t="n">
+        <v>423.584800449672</v>
+      </c>
+      <c r="L95" t="n">
+        <v>423.584800449672</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>22</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C96" t="n">
+        <v>120</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0.00264661829021004</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.999943998510305</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G96" t="n">
+        <v>31.5221809256976</v>
+      </c>
+      <c r="H96" t="n">
+        <v>25</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.00000173650187915661</v>
+      </c>
+      <c r="K96" t="n">
+        <v>691.944631498715</v>
+      </c>
+      <c r="L96" t="n">
+        <v>691.944631498715</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>22</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C97" t="n">
+        <v>120</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.00450907969787291</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.999482089700575</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G97" t="n">
+        <v>41.2209430722728</v>
+      </c>
+      <c r="H97" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.00000291738444958433</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1520.16740554049</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1520.16740554049</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>22</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C98" t="n">
+        <v>120</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.00406469420132773</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.99992550929761</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G98" t="n">
+        <v>41.4259908977818</v>
+      </c>
+      <c r="H98" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.00000266335631053549</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1394.70386978331</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1394.70386978331</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C99" t="n">
+        <v>120</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.00558277560292247</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.999971097950207</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G99" t="n">
+        <v>41.7677372736301</v>
+      </c>
+      <c r="H99" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.00000368523621171266</v>
+      </c>
+      <c r="K99" t="n">
+        <v>1945.74582627245</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1945.74582627245</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C100" t="n">
+        <v>120</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.00739360202956576</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.99991879720797</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G100" t="n">
+        <v>41.4943401729515</v>
+      </c>
+      <c r="H100" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.00000484621892500484</v>
+      </c>
+      <c r="K100" t="n">
+        <v>2541.97761269932</v>
+      </c>
+      <c r="L100" t="n">
+        <v>2541.97761269932</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>23</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C101" t="n">
+        <v>120</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.00421916128099173</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.947130565170371</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G101" t="n">
+        <v>11.5436877936052</v>
+      </c>
+      <c r="H101" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.0000027225991881261</v>
+      </c>
+      <c r="K101" t="n">
+        <v>397.290437761417</v>
+      </c>
+      <c r="L101" t="n">
+        <v>397.290437761417</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>23</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C102" t="n">
+        <v>120</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.0197139072076954</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.98832983632023</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G102" t="n">
+        <v>12.0221327197928</v>
+      </c>
+      <c r="H102" t="n">
+        <v>31</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.0000126794185032784</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1926.90668700788</v>
+      </c>
+      <c r="L102" t="n">
+        <v>1926.90668700788</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>23</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C103" t="n">
+        <v>120</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.0163086735388327</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.999960460481589</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G103" t="n">
+        <v>22.6436100811584</v>
+      </c>
+      <c r="H103" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.0000105552403320054</v>
+      </c>
+      <c r="K103" t="n">
+        <v>3021.29841712424</v>
+      </c>
+      <c r="L103" t="n">
+        <v>3021.29841712424</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>23</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C104" t="n">
+        <v>120</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.00535165433477847</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.99998480555155</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G104" t="n">
+        <v>21.8234187791225</v>
+      </c>
+      <c r="H104" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.00000346942041323482</v>
+      </c>
+      <c r="K104" t="n">
+        <v>957.104912247124</v>
+      </c>
+      <c r="L104" t="n">
+        <v>957.104912247124</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>23</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C105" t="n">
+        <v>120</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.00622855374882743</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.999973682107512</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G105" t="n">
+        <v>31.9322765767156</v>
+      </c>
+      <c r="H105" t="n">
+        <v>25</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.00000408668500828974</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1649.6084629323</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1649.6084629323</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C106" t="n">
+        <v>120</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.00447908471684053</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.999906874256435</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G106" t="n">
+        <v>41.9044358239695</v>
+      </c>
+      <c r="H106" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.00000290663405283213</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1539.67899281552</v>
+      </c>
+      <c r="L106" t="n">
+        <v>1539.67899281552</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>23</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C107" t="n">
+        <v>120</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.00702751134805582</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.999995386166255</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G107" t="n">
+        <v>41.9727850991391</v>
+      </c>
+      <c r="H107" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.00000463578801631824</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2459.63795093809</v>
+      </c>
+      <c r="L107" t="n">
+        <v>2459.63795093809</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>23</v>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C108" t="n">
+        <v>120</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.00561591762904755</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.999974340252656</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G108" t="n">
+        <v>42.4512300253268</v>
+      </c>
+      <c r="H108" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.00000372093198745085</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1996.741477782</v>
+      </c>
+      <c r="L108" t="n">
+        <v>1996.741477782</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>23</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C109" t="n">
+        <v>120</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.010938263439281</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.999961539134092</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G109" t="n">
+        <v>42.2803568374026</v>
+      </c>
+      <c r="H109" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.0000071985651442055</v>
+      </c>
+      <c r="K109" t="n">
+        <v>3847.37405848995</v>
+      </c>
+      <c r="L109" t="n">
+        <v>3847.37405848995</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>24</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C110" t="n">
+        <v>120</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.00599421202276116</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.860308996425885</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G110" t="n">
+        <v>11.5436877936052</v>
+      </c>
+      <c r="H110" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.00000386802866724952</v>
+      </c>
+      <c r="K110" t="n">
+        <v>564.435194569703</v>
+      </c>
+      <c r="L110" t="n">
+        <v>564.435194569703</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>24</v>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C111" t="n">
+        <v>120</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.0157914746199781</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.987130903251311</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G111" t="n">
+        <v>12.0392200385852</v>
+      </c>
+      <c r="H111" t="n">
+        <v>31</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.0000101566226005387</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1545.70814869222</v>
+      </c>
+      <c r="L111" t="n">
+        <v>1545.70814869222</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>24</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C112" t="n">
+        <v>120</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.0208697229339058</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.999949076541245</v>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G112" t="n">
+        <v>22.6436100811584</v>
+      </c>
+      <c r="H112" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.0000134804526306134</v>
+      </c>
+      <c r="K112" t="n">
+        <v>3858.60188057439</v>
+      </c>
+      <c r="L112" t="n">
+        <v>3858.60188057439</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>24</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C113" t="n">
+        <v>120</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.000425599785259446</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.999570378251626</v>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G113" t="n">
+        <v>21.8234187791225</v>
+      </c>
+      <c r="H113" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.000000275090905828279</v>
+      </c>
+      <c r="K113" t="n">
+        <v>75.8890033270052</v>
+      </c>
+      <c r="L113" t="n">
+        <v>75.8890033270052</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>24</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C114" t="n">
+        <v>120</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.0059926698238845</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.999969480722856</v>
+      </c>
+      <c r="F114" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G114" t="n">
+        <v>32.2398483149791</v>
+      </c>
+      <c r="H114" t="n">
+        <v>24</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.0000039451553844682</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1607.81816898261</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1607.81816898261</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>24</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C115" t="n">
+        <v>120</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.00190458998103238</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.999808839282718</v>
+      </c>
+      <c r="F115" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G115" t="n">
+        <v>41.8531738675922</v>
+      </c>
+      <c r="H115" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.00000123105180326694</v>
+      </c>
+      <c r="K115" t="n">
+        <v>651.305214716471</v>
+      </c>
+      <c r="L115" t="n">
+        <v>651.305214716471</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>24</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C116" t="n">
+        <v>120</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.00912464955968026</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.999959392258764</v>
+      </c>
+      <c r="F116" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G116" t="n">
+        <v>41.9727850991391</v>
+      </c>
+      <c r="H116" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.00000599895275991097</v>
+      </c>
+      <c r="K116" t="n">
+        <v>3182.90047392644</v>
+      </c>
+      <c r="L116" t="n">
+        <v>3182.90047392644</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>24</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C117" t="n">
+        <v>120</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.00298365138329363</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.999892221424185</v>
+      </c>
+      <c r="F117" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G117" t="n">
+        <v>42.4512300253268</v>
+      </c>
+      <c r="H117" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.00000196488932147294</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1054.40680471126</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1054.40680471126</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>24</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C118" t="n">
+        <v>120</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.0101789808021011</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.999463953119799</v>
+      </c>
+      <c r="F118" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G118" t="n">
+        <v>42.4854046629116</v>
+      </c>
+      <c r="H118" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.00000668312853773105</v>
+      </c>
+      <c r="K118" t="n">
+        <v>3589.214407389</v>
+      </c>
+      <c r="L118" t="n">
+        <v>3589.214407389</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>25</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C119" t="n">
+        <v>120</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.00478666316826988</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.981004662017986</v>
+      </c>
+      <c r="F119" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G119" t="n">
+        <v>11.4582511996431</v>
+      </c>
+      <c r="H119" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.00000308880471445296</v>
+      </c>
+      <c r="K119" t="n">
+        <v>447.392417911663</v>
+      </c>
+      <c r="L119" t="n">
+        <v>447.392417911663</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>25</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C120" t="n">
+        <v>120</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.0275288983654107</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.997358018395443</v>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G120" t="n">
+        <v>11.8170848942838</v>
+      </c>
+      <c r="H120" t="n">
+        <v>31</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.0000177057961991931</v>
+      </c>
+      <c r="K120" t="n">
+        <v>2644.87800920049</v>
+      </c>
+      <c r="L120" t="n">
+        <v>2644.87800920049</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>25</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C121" t="n">
+        <v>120</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.0155541222754531</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.9999887195311</v>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G121" t="n">
+        <v>22.6436100811584</v>
+      </c>
+      <c r="H121" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.0000099875375235413</v>
+      </c>
+      <c r="K121" t="n">
+        <v>2858.8009710539</v>
+      </c>
+      <c r="L121" t="n">
+        <v>2858.8009710539</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>25</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C122" t="n">
+        <v>120</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.00433339029264327</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.999974757447347</v>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G122" t="n">
+        <v>21.4816724032742</v>
+      </c>
+      <c r="H122" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.00000281022246904038</v>
+      </c>
+      <c r="K122" t="n">
+        <v>763.112592784348</v>
+      </c>
+      <c r="L122" t="n">
+        <v>763.112592784348</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>25</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C123" t="n">
+        <v>120</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.00253876915526875</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.999940479434039</v>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G123" t="n">
+        <v>32.0348004894701</v>
+      </c>
+      <c r="H123" t="n">
+        <v>25</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.0000016657397952612</v>
+      </c>
+      <c r="K123" t="n">
+        <v>674.542028148127</v>
+      </c>
+      <c r="L123" t="n">
+        <v>674.542028148127</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>25</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C124" t="n">
+        <v>120</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.00511119739466197</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0.999993211124916</v>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G124" t="n">
+        <v>41.6310387232908</v>
+      </c>
+      <c r="H124" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.0000033146337606757</v>
+      </c>
+      <c r="K124" t="n">
+        <v>1744.34596755931</v>
+      </c>
+      <c r="L124" t="n">
+        <v>1744.34596755931</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>25</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C125" t="n">
+        <v>120</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.00326489306665763</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.999949912933038</v>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G125" t="n">
+        <v>42.1094836494784</v>
+      </c>
+      <c r="H125" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.00000214865417711539</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1143.7372540643</v>
+      </c>
+      <c r="L125" t="n">
+        <v>1143.7372540643</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>25</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C126" t="n">
+        <v>120</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.00738367139144088</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.999948158248952</v>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G126" t="n">
+        <v>42.1778329246481</v>
+      </c>
+      <c r="H126" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.00000487896392909614</v>
+      </c>
+      <c r="K126" t="n">
+        <v>2601.30753317707</v>
+      </c>
+      <c r="L126" t="n">
+        <v>2601.30753317707</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>25</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C127" t="n">
+        <v>120</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.00691106892564838</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.999964096924581</v>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G127" t="n">
+        <v>42.2803568374026</v>
+      </c>
+      <c r="H127" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.00000455897527854346</v>
+      </c>
+      <c r="K127" t="n">
+        <v>2436.60825019887</v>
+      </c>
+      <c r="L127" t="n">
+        <v>2436.60825019887</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>26</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C128" t="n">
+        <v>120</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.0096080539378133</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.916445865386328</v>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="G128" t="n">
+        <v>10.7747584479465</v>
+      </c>
+      <c r="H128" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.00000620001893940719</v>
+      </c>
+      <c r="K128" t="n">
+        <v>844.462537825576</v>
+      </c>
+      <c r="L128" t="n">
+        <v>844.462537825576</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>26</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C129" t="n">
+        <v>120</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.0274576725918019</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.988518438134602</v>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="G129" t="n">
+        <v>11.6803863439445</v>
+      </c>
+      <c r="H129" t="n">
+        <v>31</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.0000176599858287632</v>
+      </c>
+      <c r="K129" t="n">
+        <v>2607.51843632838</v>
+      </c>
+      <c r="L129" t="n">
+        <v>2607.51843632838</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>26</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C130" t="n">
+        <v>120</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.00673608323534089</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.999917104483562</v>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="G130" t="n">
+        <v>21.9601173294618</v>
+      </c>
+      <c r="H130" t="n">
+        <v>30.2</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.00000434388640999998</v>
+      </c>
+      <c r="K130" t="n">
+        <v>1205.84904980573</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1205.84904980573</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>26</v>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C131" t="n">
+        <v>120</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.00223921972700177</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.99990077975205</v>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="G131" t="n">
+        <v>21.4133231281045</v>
+      </c>
+      <c r="H131" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.00000145746117794117</v>
+      </c>
+      <c r="K131" t="n">
+        <v>394.51261524864</v>
+      </c>
+      <c r="L131" t="n">
+        <v>394.51261524864</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>26</v>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C132" t="n">
+        <v>120</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.00114137956916641</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.999819583231245</v>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="G132" t="n">
+        <v>31.3513077377735</v>
+      </c>
+      <c r="H132" t="n">
+        <v>25</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.000000748883121536635</v>
+      </c>
+      <c r="K132" t="n">
+        <v>296.790183728622</v>
+      </c>
+      <c r="L132" t="n">
+        <v>296.790183728622</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>26</v>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C133" t="n">
+        <v>120</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.00303728508128978</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.999716967865183</v>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="G133" t="n">
+        <v>41.4259908977818</v>
+      </c>
+      <c r="H133" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J133" t="n">
         <v>0.00000196578059604244</v>
       </c>
-      <c r="K61" t="n">
+      <c r="K133" t="n">
         <v>1029.40856752812</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L133" t="n">
         <v>1029.40856752812</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>26</v>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C134" t="n">
+        <v>120</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.00239836406923181</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.999852817414187</v>
+      </c>
+      <c r="F134" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="G134" t="n">
+        <v>41.3405543038197</v>
+      </c>
+      <c r="H134" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.00000157467389580334</v>
+      </c>
+      <c r="K134" t="n">
+        <v>822.899413189293</v>
+      </c>
+      <c r="L134" t="n">
+        <v>822.899413189293</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>26</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C135" t="n">
+        <v>120</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.00312710623697268</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.999944816943138</v>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="G135" t="n">
+        <v>41.9727850991391</v>
+      </c>
+      <c r="H135" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.00000206074996738115</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1093.38451398619</v>
+      </c>
+      <c r="L135" t="n">
+        <v>1093.38451398619</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>26</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C136" t="n">
+        <v>120</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.00764029458545373</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.999925813252367</v>
+      </c>
+      <c r="F136" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="G136" t="n">
+        <v>41.5285148105363</v>
+      </c>
+      <c r="H136" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.00000683492751696629</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.00000500623805644996</v>
+      </c>
+      <c r="K136" t="n">
+        <v>2628.07482556948</v>
+      </c>
+      <c r="L136" t="n">
+        <v>2628.07482556948</v>
       </c>
     </row>
   </sheetData>

--- a/Computed_Flux/all_fluxes.xlsx
+++ b/Computed_Flux/all_fluxes.xlsx
@@ -598,16 +598,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>45810</v>
+        <v>45901</v>
       </c>
       <c r="C14" t="n">
-        <v>887.972894054391</v>
+        <v>1642.20847750066</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -615,10 +615,10 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>45817</v>
+        <v>45810</v>
       </c>
       <c r="C15" t="n">
-        <v>3620.01402513419</v>
+        <v>887.972894054391</v>
       </c>
       <c r="D15" t="s">
         <v>7</v>
@@ -629,10 +629,10 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>45826</v>
+        <v>45817</v>
       </c>
       <c r="C16" t="n">
-        <v>5848.12551989594</v>
+        <v>3620.01402513419</v>
       </c>
       <c r="D16" t="s">
         <v>7</v>
@@ -643,10 +643,10 @@
         <v>6</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>45835</v>
+        <v>45826</v>
       </c>
       <c r="C17" t="n">
-        <v>795.27107195837</v>
+        <v>5848.12551989594</v>
       </c>
       <c r="D17" t="s">
         <v>7</v>
@@ -657,10 +657,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>45842</v>
+        <v>45835</v>
       </c>
       <c r="C18" t="n">
-        <v>2863.65866842687</v>
+        <v>795.27107195837</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -671,10 +671,10 @@
         <v>6</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>45849</v>
+        <v>45842</v>
       </c>
       <c r="C19" t="n">
-        <v>582.771258652471</v>
+        <v>2863.65866842687</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -685,10 +685,10 @@
         <v>6</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>45856</v>
+        <v>45849</v>
       </c>
       <c r="C20" t="n">
-        <v>3774.37460704209</v>
+        <v>582.771258652471</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -699,10 +699,10 @@
         <v>6</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>45863</v>
+        <v>45856</v>
       </c>
       <c r="C21" t="n">
-        <v>980.83008292323</v>
+        <v>3774.37460704209</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -713,10 +713,10 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>45873</v>
+        <v>45863</v>
       </c>
       <c r="C22" t="n">
-        <v>3776.52151072127</v>
+        <v>980.83008292323</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -727,10 +727,10 @@
         <v>6</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>45880</v>
+        <v>45873</v>
       </c>
       <c r="C23" t="n">
-        <v>4118.93954141025</v>
+        <v>3776.52151072127</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -741,10 +741,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>45887</v>
+        <v>45880</v>
       </c>
       <c r="C24" t="n">
-        <v>3648.23270392578</v>
+        <v>4118.93954141025</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -755,10 +755,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>45894</v>
+        <v>45887</v>
       </c>
       <c r="C25" t="n">
-        <v>2828.4104784591</v>
+        <v>3648.23270392578</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -766,30 +766,30 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>45810</v>
+        <v>45894</v>
       </c>
       <c r="C26" t="n">
-        <v>1114.95841751639</v>
+        <v>2828.4104784591</v>
       </c>
       <c r="D26" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>45817</v>
+        <v>45901</v>
       </c>
       <c r="C27" t="n">
-        <v>3967.21046532345</v>
+        <v>1609.55976707164</v>
       </c>
       <c r="D27" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28">
@@ -797,10 +797,10 @@
         <v>8</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>45826</v>
+        <v>45810</v>
       </c>
       <c r="C28" t="n">
-        <v>3404.56710734529</v>
+        <v>1114.95841751639</v>
       </c>
       <c r="D28" t="s">
         <v>9</v>
@@ -811,10 +811,10 @@
         <v>8</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>45835</v>
+        <v>45817</v>
       </c>
       <c r="C29" t="n">
-        <v>1999.33410190424</v>
+        <v>3967.21046532345</v>
       </c>
       <c r="D29" t="s">
         <v>9</v>
@@ -825,10 +825,10 @@
         <v>8</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>45842</v>
+        <v>45826</v>
       </c>
       <c r="C30" t="n">
-        <v>529.656630645944</v>
+        <v>3404.56710734529</v>
       </c>
       <c r="D30" t="s">
         <v>9</v>
@@ -839,10 +839,10 @@
         <v>8</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>45849</v>
+        <v>45835</v>
       </c>
       <c r="C31" t="n">
-        <v>4816.73679818835</v>
+        <v>1999.33410190424</v>
       </c>
       <c r="D31" t="s">
         <v>9</v>
@@ -853,10 +853,10 @@
         <v>8</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>45856</v>
+        <v>45842</v>
       </c>
       <c r="C32" t="n">
-        <v>2193.24328610956</v>
+        <v>529.656630645944</v>
       </c>
       <c r="D32" t="s">
         <v>9</v>
@@ -867,10 +867,10 @@
         <v>8</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>45863</v>
+        <v>45849</v>
       </c>
       <c r="C33" t="n">
-        <v>3643.24026825053</v>
+        <v>4816.73679818835</v>
       </c>
       <c r="D33" t="s">
         <v>9</v>
@@ -881,10 +881,10 @@
         <v>8</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>45873</v>
+        <v>45856</v>
       </c>
       <c r="C34" t="n">
-        <v>3128.79369665423</v>
+        <v>2193.24328610956</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -895,10 +895,10 @@
         <v>8</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>45880</v>
+        <v>45863</v>
       </c>
       <c r="C35" t="n">
-        <v>4586.82933528355</v>
+        <v>3643.24026825053</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -909,10 +909,10 @@
         <v>8</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>45887</v>
+        <v>45873</v>
       </c>
       <c r="C36" t="n">
-        <v>3394.16343445068</v>
+        <v>3128.79369665423</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -923,10 +923,10 @@
         <v>8</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>45894</v>
+        <v>45880</v>
       </c>
       <c r="C37" t="n">
-        <v>2703.9092133905</v>
+        <v>4586.82933528355</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -934,44 +934,44 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>45810</v>
+        <v>45887</v>
       </c>
       <c r="C38" t="n">
-        <v>896.001226735543</v>
+        <v>3394.16343445068</v>
       </c>
       <c r="D38" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>45817</v>
+        <v>45894</v>
       </c>
       <c r="C39" t="n">
-        <v>2030.70030492232</v>
+        <v>2703.9092133905</v>
       </c>
       <c r="D39" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>45826</v>
+        <v>45901</v>
       </c>
       <c r="C40" t="n">
-        <v>7084.27944063735</v>
+        <v>1785.31900434777</v>
       </c>
       <c r="D40" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -979,10 +979,10 @@
         <v>10</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>45835</v>
+        <v>45810</v>
       </c>
       <c r="C41" t="n">
-        <v>911.65002482044</v>
+        <v>896.001226735543</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -993,10 +993,10 @@
         <v>10</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>45842</v>
+        <v>45817</v>
       </c>
       <c r="C42" t="n">
-        <v>923.42600524363</v>
+        <v>2030.70030492232</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
@@ -1007,10 +1007,10 @@
         <v>10</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>45849</v>
+        <v>45826</v>
       </c>
       <c r="C43" t="n">
-        <v>2298.37541327764</v>
+        <v>7084.27944063735</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -1021,10 +1021,10 @@
         <v>10</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>45856</v>
+        <v>45835</v>
       </c>
       <c r="C44" t="n">
-        <v>2548.92674654963</v>
+        <v>911.65002482044</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
@@ -1035,10 +1035,10 @@
         <v>10</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>45863</v>
+        <v>45842</v>
       </c>
       <c r="C45" t="n">
-        <v>2284.96228575287</v>
+        <v>923.42600524363</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -1049,10 +1049,10 @@
         <v>10</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>45873</v>
+        <v>45849</v>
       </c>
       <c r="C46" t="n">
-        <v>2405.49680671009</v>
+        <v>2298.37541327764</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
@@ -1063,10 +1063,10 @@
         <v>10</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>45880</v>
+        <v>45856</v>
       </c>
       <c r="C47" t="n">
-        <v>5789.58956490831</v>
+        <v>2548.92674654963</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
@@ -1077,10 +1077,10 @@
         <v>10</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>45887</v>
+        <v>45863</v>
       </c>
       <c r="C48" t="n">
-        <v>3313.54847929235</v>
+        <v>2284.96228575287</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
@@ -1091,10 +1091,10 @@
         <v>10</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>45894</v>
+        <v>45873</v>
       </c>
       <c r="C49" t="n">
-        <v>3187.1648559333</v>
+        <v>2405.49680671009</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
@@ -1102,58 +1102,58 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>45810</v>
+        <v>45880</v>
       </c>
       <c r="C50" t="n">
-        <v>605.276401347038</v>
+        <v>5789.58956490831</v>
       </c>
       <c r="D50" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>45817</v>
+        <v>45887</v>
       </c>
       <c r="C51" t="n">
-        <v>3254.15705318998</v>
+        <v>3313.54847929235</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>45826</v>
+        <v>45894</v>
       </c>
       <c r="C52" t="n">
-        <v>5494.93846571461</v>
+        <v>3187.1648559333</v>
       </c>
       <c r="D52" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>45835</v>
+        <v>45901</v>
       </c>
       <c r="C53" t="n">
-        <v>493.831746277201</v>
+        <v>1469.24426484684</v>
       </c>
       <c r="D53" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
@@ -1161,10 +1161,10 @@
         <v>11</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>45842</v>
+        <v>45810</v>
       </c>
       <c r="C54" t="n">
-        <v>1033.1066084577</v>
+        <v>605.276401347038</v>
       </c>
       <c r="D54" t="s">
         <v>7</v>
@@ -1175,10 +1175,10 @@
         <v>11</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>45849</v>
+        <v>45817</v>
       </c>
       <c r="C55" t="n">
-        <v>809.578051527371</v>
+        <v>3254.15705318998</v>
       </c>
       <c r="D55" t="s">
         <v>7</v>
@@ -1189,10 +1189,10 @@
         <v>11</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>45856</v>
+        <v>45826</v>
       </c>
       <c r="C56" t="n">
-        <v>2699.12605710809</v>
+        <v>5494.93846571461</v>
       </c>
       <c r="D56" t="s">
         <v>7</v>
@@ -1203,10 +1203,10 @@
         <v>11</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>45863</v>
+        <v>45835</v>
       </c>
       <c r="C57" t="n">
-        <v>1219.60301108964</v>
+        <v>493.831746277201</v>
       </c>
       <c r="D57" t="s">
         <v>7</v>
@@ -1217,10 +1217,10 @@
         <v>11</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>45873</v>
+        <v>45842</v>
       </c>
       <c r="C58" t="n">
-        <v>3429.90174797312</v>
+        <v>1033.1066084577</v>
       </c>
       <c r="D58" t="s">
         <v>7</v>
@@ -1231,10 +1231,10 @@
         <v>11</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>45880</v>
+        <v>45849</v>
       </c>
       <c r="C59" t="n">
-        <v>3447.29762872426</v>
+        <v>809.578051527371</v>
       </c>
       <c r="D59" t="s">
         <v>7</v>
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>45887</v>
+        <v>45856</v>
       </c>
       <c r="C60" t="n">
-        <v>2971.31194167402</v>
+        <v>2699.12605710809</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
@@ -1259,10 +1259,10 @@
         <v>11</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>45894</v>
+        <v>45863</v>
       </c>
       <c r="C61" t="n">
-        <v>2128.81048195735</v>
+        <v>1219.60301108964</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
@@ -1270,72 +1270,72 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>45810</v>
+        <v>45873</v>
       </c>
       <c r="C62" t="n">
-        <v>829.274264965441</v>
+        <v>3429.90174797312</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>45817</v>
+        <v>45880</v>
       </c>
       <c r="C63" t="n">
-        <v>2034.26328932924</v>
+        <v>3447.29762872426</v>
       </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>45826</v>
+        <v>45887</v>
       </c>
       <c r="C64" t="n">
-        <v>3085.76309059706</v>
+        <v>2971.31194167402</v>
       </c>
       <c r="D64" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>45835</v>
+        <v>45894</v>
       </c>
       <c r="C65" t="n">
-        <v>2113.86708643315</v>
+        <v>2128.81048195735</v>
       </c>
       <c r="D65" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>45842</v>
+        <v>45901</v>
       </c>
       <c r="C66" t="n">
-        <v>1158.7597584648</v>
+        <v>1885.52718940828</v>
       </c>
       <c r="D66" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67">
@@ -1343,10 +1343,10 @@
         <v>12</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>45849</v>
+        <v>45810</v>
       </c>
       <c r="C67" t="n">
-        <v>3804.85995259262</v>
+        <v>829.274264965441</v>
       </c>
       <c r="D67" t="s">
         <v>9</v>
@@ -1357,10 +1357,10 @@
         <v>12</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>45856</v>
+        <v>45817</v>
       </c>
       <c r="C68" t="n">
-        <v>1889.8067251411</v>
+        <v>2034.26328932924</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
@@ -1371,10 +1371,10 @@
         <v>12</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>45863</v>
+        <v>45826</v>
       </c>
       <c r="C69" t="n">
-        <v>4061.45488430826</v>
+        <v>3085.76309059706</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
@@ -1385,10 +1385,10 @@
         <v>12</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>45873</v>
+        <v>45835</v>
       </c>
       <c r="C70" t="n">
-        <v>2808.60882816944</v>
+        <v>2113.86708643315</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
@@ -1399,10 +1399,10 @@
         <v>12</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>45880</v>
+        <v>45842</v>
       </c>
       <c r="C71" t="n">
-        <v>4334.8959831226</v>
+        <v>1158.7597584648</v>
       </c>
       <c r="D71" t="s">
         <v>9</v>
@@ -1413,10 +1413,10 @@
         <v>12</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>45887</v>
+        <v>45849</v>
       </c>
       <c r="C72" t="n">
-        <v>1799.96285583044</v>
+        <v>3804.85995259262</v>
       </c>
       <c r="D72" t="s">
         <v>9</v>
@@ -1427,10 +1427,10 @@
         <v>12</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>45894</v>
+        <v>45856</v>
       </c>
       <c r="C73" t="n">
-        <v>3245.54806926349</v>
+        <v>1889.8067251411</v>
       </c>
       <c r="D73" t="s">
         <v>9</v>
@@ -1438,86 +1438,86 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>45810</v>
+        <v>45863</v>
       </c>
       <c r="C74" t="n">
-        <v>926.247921016511</v>
+        <v>4061.45488430826</v>
       </c>
       <c r="D74" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>45817</v>
+        <v>45873</v>
       </c>
       <c r="C75" t="n">
-        <v>1013.90634494399</v>
+        <v>2808.60882816944</v>
       </c>
       <c r="D75" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>45826</v>
+        <v>45880</v>
       </c>
       <c r="C76" t="n">
-        <v>2492.6382352641</v>
+        <v>4334.8959831226</v>
       </c>
       <c r="D76" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>45835</v>
+        <v>45887</v>
       </c>
       <c r="C77" t="n">
-        <v>208.353459554264</v>
+        <v>1799.96285583044</v>
       </c>
       <c r="D77" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>45842</v>
+        <v>45894</v>
       </c>
       <c r="C78" t="n">
-        <v>642.842381753608</v>
+        <v>3245.54806926349</v>
       </c>
       <c r="D78" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>45849</v>
+        <v>45901</v>
       </c>
       <c r="C79" t="n">
-        <v>708.264946681898</v>
+        <v>1181.54431177802</v>
       </c>
       <c r="D79" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
@@ -1525,10 +1525,10 @@
         <v>13</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>45856</v>
+        <v>45810</v>
       </c>
       <c r="C80" t="n">
-        <v>1297.74874736552</v>
+        <v>926.247921016511</v>
       </c>
       <c r="D80" t="s">
         <v>5</v>
@@ -1539,10 +1539,10 @@
         <v>13</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>45863</v>
+        <v>45817</v>
       </c>
       <c r="C81" t="n">
-        <v>1282.98566492001</v>
+        <v>1013.90634494399</v>
       </c>
       <c r="D81" t="s">
         <v>5</v>
@@ -1553,10 +1553,10 @@
         <v>13</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>45873</v>
+        <v>45826</v>
       </c>
       <c r="C82" t="n">
-        <v>3039.25791166093</v>
+        <v>2492.6382352641</v>
       </c>
       <c r="D82" t="s">
         <v>5</v>
@@ -1567,10 +1567,10 @@
         <v>13</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>45880</v>
+        <v>45835</v>
       </c>
       <c r="C83" t="n">
-        <v>4775.20972744648</v>
+        <v>208.353459554264</v>
       </c>
       <c r="D83" t="s">
         <v>5</v>
@@ -1581,10 +1581,10 @@
         <v>13</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>45887</v>
+        <v>45842</v>
       </c>
       <c r="C84" t="n">
-        <v>2089.81926332235</v>
+        <v>642.842381753608</v>
       </c>
       <c r="D84" t="s">
         <v>5</v>
@@ -1595,10 +1595,10 @@
         <v>13</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>45894</v>
+        <v>45849</v>
       </c>
       <c r="C85" t="n">
-        <v>4752.47660961459</v>
+        <v>708.264946681898</v>
       </c>
       <c r="D85" t="s">
         <v>5</v>
@@ -1606,100 +1606,100 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>45810</v>
+        <v>45856</v>
       </c>
       <c r="C86" t="n">
-        <v>820.429289044661</v>
+        <v>1297.74874736552</v>
       </c>
       <c r="D86" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>45817</v>
+        <v>45863</v>
       </c>
       <c r="C87" t="n">
-        <v>4438.5887346754</v>
+        <v>1282.98566492001</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>45826</v>
+        <v>45873</v>
       </c>
       <c r="C88" t="n">
-        <v>3375.80821888685</v>
+        <v>3039.25791166093</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>45835</v>
+        <v>45880</v>
       </c>
       <c r="C89" t="n">
-        <v>783.186507035906</v>
+        <v>4775.20972744648</v>
       </c>
       <c r="D89" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>45842</v>
+        <v>45887</v>
       </c>
       <c r="C90" t="n">
-        <v>631.923814275014</v>
+        <v>2089.81926332235</v>
       </c>
       <c r="D90" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>45849</v>
+        <v>45894</v>
       </c>
       <c r="C91" t="n">
-        <v>1315.52124698387</v>
+        <v>4752.47660961459</v>
       </c>
       <c r="D91" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>45856</v>
+        <v>45901</v>
       </c>
       <c r="C92" t="n">
-        <v>2207.89437180403</v>
+        <v>1541.24223720587</v>
       </c>
       <c r="D92" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -1707,10 +1707,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>45863</v>
+        <v>45810</v>
       </c>
       <c r="C93" t="n">
-        <v>2258.29619366983</v>
+        <v>820.429289044661</v>
       </c>
       <c r="D93" t="s">
         <v>7</v>
@@ -1721,10 +1721,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>45873</v>
+        <v>45817</v>
       </c>
       <c r="C94" t="n">
-        <v>3728.99958287456</v>
+        <v>4438.5887346754</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
@@ -1735,10 +1735,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="1" t="n">
-        <v>45880</v>
+        <v>45826</v>
       </c>
       <c r="C95" t="n">
-        <v>3912.32265691079</v>
+        <v>3375.80821888685</v>
       </c>
       <c r="D95" t="s">
         <v>7</v>
@@ -1749,10 +1749,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="1" t="n">
-        <v>45887</v>
+        <v>45835</v>
       </c>
       <c r="C96" t="n">
-        <v>3599.81922977165</v>
+        <v>783.186507035906</v>
       </c>
       <c r="D96" t="s">
         <v>7</v>
@@ -1763,10 +1763,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>45894</v>
+        <v>45842</v>
       </c>
       <c r="C97" t="n">
-        <v>2913.7632567457</v>
+        <v>631.923814275014</v>
       </c>
       <c r="D97" t="s">
         <v>7</v>
@@ -1774,114 +1774,114 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>45810</v>
+        <v>45849</v>
       </c>
       <c r="C98" t="n">
-        <v>749.87306919933</v>
+        <v>1315.52124698387</v>
       </c>
       <c r="D98" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>45817</v>
+        <v>45856</v>
       </c>
       <c r="C99" t="n">
-        <v>4412.64180269369</v>
+        <v>2207.89437180403</v>
       </c>
       <c r="D99" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>45826</v>
+        <v>45863</v>
       </c>
       <c r="C100" t="n">
-        <v>6968.33616394737</v>
+        <v>2258.29619366983</v>
       </c>
       <c r="D100" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>45835</v>
+        <v>45873</v>
       </c>
       <c r="C101" t="n">
-        <v>1687.73157419569</v>
+        <v>3728.99958287456</v>
       </c>
       <c r="D101" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>45842</v>
+        <v>45880</v>
       </c>
       <c r="C102" t="n">
-        <v>761.833024239517</v>
+        <v>3912.32265691079</v>
       </c>
       <c r="D102" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>45849</v>
+        <v>45887</v>
       </c>
       <c r="C103" t="n">
-        <v>2588.80886828618</v>
+        <v>3599.81922977165</v>
       </c>
       <c r="D103" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>45856</v>
+        <v>45894</v>
       </c>
       <c r="C104" t="n">
-        <v>3605.2695200209</v>
+        <v>2913.7632567457</v>
       </c>
       <c r="D104" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>45863</v>
+        <v>45901</v>
       </c>
       <c r="C105" t="n">
-        <v>2464.37485564112</v>
+        <v>2488.12022404981</v>
       </c>
       <c r="D105" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -1889,10 +1889,10 @@
         <v>15</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>45873</v>
+        <v>45810</v>
       </c>
       <c r="C106" t="n">
-        <v>3566.94051479447</v>
+        <v>749.87306919933</v>
       </c>
       <c r="D106" t="s">
         <v>9</v>
@@ -1903,10 +1903,10 @@
         <v>15</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>45880</v>
+        <v>45817</v>
       </c>
       <c r="C107" t="n">
-        <v>5545.11780891709</v>
+        <v>4412.64180269369</v>
       </c>
       <c r="D107" t="s">
         <v>9</v>
@@ -1917,10 +1917,10 @@
         <v>15</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>45887</v>
+        <v>45826</v>
       </c>
       <c r="C108" t="n">
-        <v>2723.46038359217</v>
+        <v>6968.33616394737</v>
       </c>
       <c r="D108" t="s">
         <v>9</v>
@@ -1931,10 +1931,10 @@
         <v>15</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>45894</v>
+        <v>45835</v>
       </c>
       <c r="C109" t="n">
-        <v>3638.2311832252</v>
+        <v>1687.73157419569</v>
       </c>
       <c r="D109" t="s">
         <v>9</v>
@@ -1942,128 +1942,128 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>45810</v>
+        <v>45842</v>
       </c>
       <c r="C110" t="n">
-        <v>654.622171815671</v>
+        <v>761.833024239517</v>
       </c>
       <c r="D110" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>45817</v>
+        <v>45849</v>
       </c>
       <c r="C111" t="n">
-        <v>836.306701729539</v>
+        <v>2588.80886828618</v>
       </c>
       <c r="D111" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>45826</v>
+        <v>45856</v>
       </c>
       <c r="C112" t="n">
-        <v>752.809303565924</v>
+        <v>3605.2695200209</v>
       </c>
       <c r="D112" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>45835</v>
+        <v>45863</v>
       </c>
       <c r="C113" t="n">
-        <v>361.937925301449</v>
+        <v>2464.37485564112</v>
       </c>
       <c r="D113" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>45842</v>
+        <v>45873</v>
       </c>
       <c r="C114" t="n">
-        <v>274.147297459927</v>
+        <v>3566.94051479447</v>
       </c>
       <c r="D114" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>45849</v>
+        <v>45880</v>
       </c>
       <c r="C115" t="n">
-        <v>638.156969539091</v>
+        <v>5545.11780891709</v>
       </c>
       <c r="D115" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>45856</v>
+        <v>45887</v>
       </c>
       <c r="C116" t="n">
-        <v>671.100601945576</v>
+        <v>2723.46038359217</v>
       </c>
       <c r="D116" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>45863</v>
+        <v>45894</v>
       </c>
       <c r="C117" t="n">
-        <v>1126.92089194702</v>
+        <v>3638.2311832252</v>
       </c>
       <c r="D117" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>45873</v>
+        <v>45901</v>
       </c>
       <c r="C118" t="n">
-        <v>1904.69958425363</v>
+        <v>1849.60594842151</v>
       </c>
       <c r="D118" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
@@ -2071,10 +2071,10 @@
         <v>16</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>45880</v>
+        <v>45810</v>
       </c>
       <c r="C119" t="n">
-        <v>3800.93540490905</v>
+        <v>654.622171815671</v>
       </c>
       <c r="D119" t="s">
         <v>5</v>
@@ -2085,10 +2085,10 @@
         <v>16</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>45887</v>
+        <v>45817</v>
       </c>
       <c r="C120" t="n">
-        <v>2170.9732688459</v>
+        <v>836.306701729539</v>
       </c>
       <c r="D120" t="s">
         <v>5</v>
@@ -2099,10 +2099,10 @@
         <v>16</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>45894</v>
+        <v>45826</v>
       </c>
       <c r="C121" t="n">
-        <v>3307.44136835169</v>
+        <v>752.809303565924</v>
       </c>
       <c r="D121" t="s">
         <v>5</v>
@@ -2110,142 +2110,142 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>45810</v>
+        <v>45835</v>
       </c>
       <c r="C122" t="n">
-        <v>714.089199892923</v>
+        <v>361.937925301449</v>
       </c>
       <c r="D122" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>45817</v>
+        <v>45842</v>
       </c>
       <c r="C123" t="n">
-        <v>1332.31394460659</v>
+        <v>274.147297459927</v>
       </c>
       <c r="D123" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>45826</v>
+        <v>45849</v>
       </c>
       <c r="C124" t="n">
-        <v>1403.48926864965</v>
+        <v>638.156969539091</v>
       </c>
       <c r="D124" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>45835</v>
+        <v>45856</v>
       </c>
       <c r="C125" t="n">
-        <v>423.584800449672</v>
+        <v>671.100601945576</v>
       </c>
       <c r="D125" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>45842</v>
+        <v>45863</v>
       </c>
       <c r="C126" t="n">
-        <v>691.944631498715</v>
+        <v>1126.92089194702</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>45849</v>
+        <v>45873</v>
       </c>
       <c r="C127" t="n">
-        <v>1520.16740554049</v>
+        <v>1904.69958425363</v>
       </c>
       <c r="D127" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>45856</v>
+        <v>45880</v>
       </c>
       <c r="C128" t="n">
-        <v>1394.70386978331</v>
+        <v>3800.93540490905</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>45863</v>
+        <v>45887</v>
       </c>
       <c r="C129" t="n">
-        <v>1945.74582627245</v>
+        <v>2170.9732688459</v>
       </c>
       <c r="D129" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>45873</v>
+        <v>45894</v>
       </c>
       <c r="C130" t="n">
-        <v>2541.97761269932</v>
+        <v>3307.44136835169</v>
       </c>
       <c r="D130" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>45880</v>
+        <v>45901</v>
       </c>
       <c r="C131" t="n">
-        <v>3884.74955947511</v>
+        <v>988.497215490608</v>
       </c>
       <c r="D131" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132">
@@ -2253,10 +2253,10 @@
         <v>17</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>45887</v>
+        <v>45810</v>
       </c>
       <c r="C132" t="n">
-        <v>1740.78269526192</v>
+        <v>714.089199892923</v>
       </c>
       <c r="D132" t="s">
         <v>7</v>
@@ -2267,10 +2267,10 @@
         <v>17</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>45894</v>
+        <v>45817</v>
       </c>
       <c r="C133" t="n">
-        <v>2505.19645489012</v>
+        <v>1332.31394460659</v>
       </c>
       <c r="D133" t="s">
         <v>7</v>
@@ -2278,156 +2278,156 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>45810</v>
+        <v>45826</v>
       </c>
       <c r="C134" t="n">
-        <v>397.290437761417</v>
+        <v>1403.48926864965</v>
       </c>
       <c r="D134" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>45817</v>
+        <v>45835</v>
       </c>
       <c r="C135" t="n">
-        <v>1926.90668700788</v>
+        <v>423.584800449672</v>
       </c>
       <c r="D135" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>45826</v>
+        <v>45842</v>
       </c>
       <c r="C136" t="n">
-        <v>3021.29841712424</v>
+        <v>691.944631498715</v>
       </c>
       <c r="D136" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>45835</v>
+        <v>45849</v>
       </c>
       <c r="C137" t="n">
-        <v>957.104912247124</v>
+        <v>1520.16740554049</v>
       </c>
       <c r="D137" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>45842</v>
+        <v>45856</v>
       </c>
       <c r="C138" t="n">
-        <v>1649.6084629323</v>
+        <v>1394.70386978331</v>
       </c>
       <c r="D138" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>45849</v>
+        <v>45863</v>
       </c>
       <c r="C139" t="n">
-        <v>1539.67899281552</v>
+        <v>1945.74582627245</v>
       </c>
       <c r="D139" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>45856</v>
+        <v>45873</v>
       </c>
       <c r="C140" t="n">
-        <v>2459.63795093809</v>
+        <v>2541.97761269932</v>
       </c>
       <c r="D140" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>45863</v>
+        <v>45880</v>
       </c>
       <c r="C141" t="n">
-        <v>1996.741477782</v>
+        <v>3884.74955947511</v>
       </c>
       <c r="D141" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B142" s="1" t="n">
-        <v>45873</v>
+        <v>45887</v>
       </c>
       <c r="C142" t="n">
-        <v>3847.37405848995</v>
+        <v>1740.78269526192</v>
       </c>
       <c r="D142" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>45880</v>
+        <v>45894</v>
       </c>
       <c r="C143" t="n">
-        <v>2828.98818979552</v>
+        <v>2505.19645489012</v>
       </c>
       <c r="D143" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B144" s="1" t="n">
-        <v>45887</v>
+        <v>45901</v>
       </c>
       <c r="C144" t="n">
-        <v>2591.30540522796</v>
+        <v>973.643220252498</v>
       </c>
       <c r="D144" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="145">
@@ -2435,10 +2435,10 @@
         <v>18</v>
       </c>
       <c r="B145" s="1" t="n">
-        <v>45894</v>
+        <v>45810</v>
       </c>
       <c r="C145" t="n">
-        <v>1495.1664275966</v>
+        <v>397.290437761417</v>
       </c>
       <c r="D145" t="s">
         <v>9</v>
@@ -2446,505 +2446,715 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>45810</v>
+        <v>45817</v>
       </c>
       <c r="C146" t="n">
-        <v>564.435194569703</v>
+        <v>1926.90668700788</v>
       </c>
       <c r="D146" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>45817</v>
+        <v>45826</v>
       </c>
       <c r="C147" t="n">
-        <v>1545.70814869222</v>
+        <v>3021.29841712424</v>
       </c>
       <c r="D147" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>45826</v>
+        <v>45835</v>
       </c>
       <c r="C148" t="n">
-        <v>3858.60188057439</v>
+        <v>957.104912247124</v>
       </c>
       <c r="D148" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>45835</v>
+        <v>45842</v>
       </c>
       <c r="C149" t="n">
-        <v>75.8890033270052</v>
+        <v>1649.6084629323</v>
       </c>
       <c r="D149" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="C150" t="n">
-        <v>1607.81816898261</v>
+        <v>1539.67899281552</v>
       </c>
       <c r="D150" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="C151" t="n">
-        <v>651.305214716471</v>
+        <v>2459.63795093809</v>
       </c>
       <c r="D151" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B152" s="1" t="n">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="C152" t="n">
-        <v>3182.90047392644</v>
+        <v>1996.741477782</v>
       </c>
       <c r="D152" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>45863</v>
+        <v>45873</v>
       </c>
       <c r="C153" t="n">
-        <v>1054.40680471126</v>
+        <v>3847.37405848995</v>
       </c>
       <c r="D153" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B154" s="1" t="n">
-        <v>45873</v>
+        <v>45880</v>
       </c>
       <c r="C154" t="n">
-        <v>3589.214407389</v>
+        <v>2828.98818979552</v>
       </c>
       <c r="D154" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>45880</v>
+        <v>45887</v>
       </c>
       <c r="C155" t="n">
-        <v>2375.18299388371</v>
+        <v>2591.30540522796</v>
       </c>
       <c r="D155" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>45887</v>
+        <v>45894</v>
       </c>
       <c r="C156" t="n">
-        <v>2768.14096770644</v>
+        <v>1495.1664275966</v>
       </c>
       <c r="D156" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>45894</v>
+        <v>45901</v>
       </c>
       <c r="C157" t="n">
-        <v>1810.23398806605</v>
+        <v>1208.07345867435</v>
       </c>
       <c r="D157" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B158" s="1" t="n">
         <v>45810</v>
       </c>
       <c r="C158" t="n">
-        <v>447.392417911663</v>
+        <v>564.435194569703</v>
       </c>
       <c r="D158" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B159" s="1" t="n">
         <v>45817</v>
       </c>
       <c r="C159" t="n">
-        <v>2644.87800920049</v>
+        <v>1545.70814869222</v>
       </c>
       <c r="D159" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B160" s="1" t="n">
         <v>45826</v>
       </c>
       <c r="C160" t="n">
-        <v>2858.8009710539</v>
+        <v>3858.60188057439</v>
       </c>
       <c r="D160" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B161" s="1" t="n">
         <v>45835</v>
       </c>
       <c r="C161" t="n">
-        <v>763.112592784348</v>
+        <v>75.8890033270052</v>
       </c>
       <c r="D161" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B162" s="1" t="n">
         <v>45842</v>
       </c>
       <c r="C162" t="n">
-        <v>674.542028148127</v>
+        <v>1607.81816898261</v>
       </c>
       <c r="D162" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B163" s="1" t="n">
         <v>45849</v>
       </c>
       <c r="C163" t="n">
-        <v>1744.34596755931</v>
+        <v>651.305214716471</v>
       </c>
       <c r="D163" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B164" s="1" t="n">
         <v>45856</v>
       </c>
       <c r="C164" t="n">
-        <v>1143.7372540643</v>
+        <v>3182.90047392644</v>
       </c>
       <c r="D164" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B165" s="1" t="n">
         <v>45863</v>
       </c>
       <c r="C165" t="n">
-        <v>2601.30753317707</v>
+        <v>1054.40680471126</v>
       </c>
       <c r="D165" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B166" s="1" t="n">
         <v>45873</v>
       </c>
       <c r="C166" t="n">
-        <v>2436.60825019887</v>
+        <v>3589.214407389</v>
       </c>
       <c r="D166" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B167" s="1" t="n">
         <v>45880</v>
       </c>
       <c r="C167" t="n">
-        <v>3629.61304883485</v>
+        <v>2375.18299388371</v>
       </c>
       <c r="D167" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B168" s="1" t="n">
         <v>45887</v>
       </c>
       <c r="C168" t="n">
-        <v>2475.83592992463</v>
+        <v>2768.14096770644</v>
       </c>
       <c r="D168" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B169" s="1" t="n">
         <v>45894</v>
       </c>
       <c r="C169" t="n">
-        <v>2279.65892583665</v>
+        <v>1810.23398806605</v>
       </c>
       <c r="D169" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>45810</v>
+        <v>45901</v>
       </c>
       <c r="C170" t="n">
-        <v>844.462537825576</v>
+        <v>2132.26773713034</v>
       </c>
       <c r="D170" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B171" s="1" t="n">
-        <v>45817</v>
+        <v>45810</v>
       </c>
       <c r="C171" t="n">
-        <v>2607.51843632838</v>
+        <v>447.392417911663</v>
       </c>
       <c r="D171" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B172" s="1" t="n">
-        <v>45826</v>
+        <v>45817</v>
       </c>
       <c r="C172" t="n">
-        <v>1205.84904980573</v>
+        <v>2644.87800920049</v>
       </c>
       <c r="D172" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B173" s="1" t="n">
-        <v>45835</v>
+        <v>45826</v>
       </c>
       <c r="C173" t="n">
-        <v>394.51261524864</v>
+        <v>2858.8009710539</v>
       </c>
       <c r="D173" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B174" s="1" t="n">
-        <v>45842</v>
+        <v>45835</v>
       </c>
       <c r="C174" t="n">
-        <v>296.790183728622</v>
+        <v>763.112592784348</v>
       </c>
       <c r="D174" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B175" s="1" t="n">
-        <v>45849</v>
+        <v>45842</v>
       </c>
       <c r="C175" t="n">
-        <v>1029.40856752812</v>
+        <v>674.542028148127</v>
       </c>
       <c r="D175" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>45856</v>
+        <v>45849</v>
       </c>
       <c r="C176" t="n">
-        <v>822.899413189293</v>
+        <v>1744.34596755931</v>
       </c>
       <c r="D176" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>45863</v>
+        <v>45856</v>
       </c>
       <c r="C177" t="n">
-        <v>1093.38451398619</v>
+        <v>1143.7372540643</v>
       </c>
       <c r="D177" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B178" s="1" t="n">
-        <v>45873</v>
+        <v>45863</v>
       </c>
       <c r="C178" t="n">
-        <v>2628.07482556948</v>
+        <v>2601.30753317707</v>
       </c>
       <c r="D178" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B179" s="1" t="n">
-        <v>45880</v>
+        <v>45873</v>
       </c>
       <c r="C179" t="n">
-        <v>2995.86132481368</v>
+        <v>2436.60825019887</v>
       </c>
       <c r="D179" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B180" s="1" t="n">
-        <v>45887</v>
+        <v>45880</v>
       </c>
       <c r="C180" t="n">
-        <v>2000.21497594218</v>
+        <v>3629.61304883485</v>
       </c>
       <c r="D180" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
+        <v>20</v>
+      </c>
+      <c r="B181" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="C181" t="n">
+        <v>2475.83592992463</v>
+      </c>
+      <c r="D181" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>20</v>
+      </c>
+      <c r="B182" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="C182" t="n">
+        <v>2279.65892583665</v>
+      </c>
+      <c r="D182" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>20</v>
+      </c>
+      <c r="B183" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C183" t="n">
+        <v>998.259977017587</v>
+      </c>
+      <c r="D183" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
         <v>21</v>
       </c>
-      <c r="B181" s="1" t="n">
+      <c r="B184" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C184" t="n">
+        <v>844.462537825576</v>
+      </c>
+      <c r="D184" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>21</v>
+      </c>
+      <c r="B185" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C185" t="n">
+        <v>2607.51843632838</v>
+      </c>
+      <c r="D185" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>21</v>
+      </c>
+      <c r="B186" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C186" t="n">
+        <v>1205.84904980573</v>
+      </c>
+      <c r="D186" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>21</v>
+      </c>
+      <c r="B187" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C187" t="n">
+        <v>394.51261524864</v>
+      </c>
+      <c r="D187" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>21</v>
+      </c>
+      <c r="B188" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C188" t="n">
+        <v>296.790183728622</v>
+      </c>
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>21</v>
+      </c>
+      <c r="B189" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C189" t="n">
+        <v>1029.40856752812</v>
+      </c>
+      <c r="D189" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>21</v>
+      </c>
+      <c r="B190" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C190" t="n">
+        <v>822.899413189293</v>
+      </c>
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>21</v>
+      </c>
+      <c r="B191" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C191" t="n">
+        <v>1093.38451398619</v>
+      </c>
+      <c r="D191" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>21</v>
+      </c>
+      <c r="B192" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C192" t="n">
+        <v>2628.07482556948</v>
+      </c>
+      <c r="D192" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>21</v>
+      </c>
+      <c r="B193" s="1" t="n">
+        <v>45880</v>
+      </c>
+      <c r="C193" t="n">
+        <v>2995.86132481368</v>
+      </c>
+      <c r="D193" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>21</v>
+      </c>
+      <c r="B194" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="C194" t="n">
+        <v>2000.21497594218</v>
+      </c>
+      <c r="D194" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>21</v>
+      </c>
+      <c r="B195" s="1" t="n">
         <v>45894</v>
       </c>
-      <c r="C181" t="n">
+      <c r="C195" t="n">
         <v>1879.36457990422</v>
       </c>
-      <c r="D181" t="s">
+      <c r="D195" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>21</v>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C196" t="n">
+        <v>967.384492520583</v>
+      </c>
+      <c r="D196" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Computed_Flux/all_fluxes.xlsx
+++ b/Computed_Flux/all_fluxes.xlsx
@@ -612,44 +612,44 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>45810</v>
+        <v>45908</v>
       </c>
       <c r="C15" t="n">
-        <v>887.972894054391</v>
+        <v>825.497971906722</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B16" s="1" t="n">
-        <v>45817</v>
+        <v>45912</v>
       </c>
       <c r="C16" t="n">
-        <v>3620.01402513419</v>
+        <v>5094.94811274734</v>
       </c>
       <c r="D16" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B17" s="1" t="n">
-        <v>45826</v>
+        <v>45918</v>
       </c>
       <c r="C17" t="n">
-        <v>5848.12551989594</v>
+        <v>29.1384604509441</v>
       </c>
       <c r="D17" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -657,10 +657,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>45835</v>
+        <v>45810</v>
       </c>
       <c r="C18" t="n">
-        <v>795.27107195837</v>
+        <v>887.972894054391</v>
       </c>
       <c r="D18" t="s">
         <v>7</v>
@@ -671,10 +671,10 @@
         <v>6</v>
       </c>
       <c r="B19" s="1" t="n">
-        <v>45842</v>
+        <v>45817</v>
       </c>
       <c r="C19" t="n">
-        <v>2863.65866842687</v>
+        <v>3620.01402513419</v>
       </c>
       <c r="D19" t="s">
         <v>7</v>
@@ -685,10 +685,10 @@
         <v>6</v>
       </c>
       <c r="B20" s="1" t="n">
-        <v>45849</v>
+        <v>45826</v>
       </c>
       <c r="C20" t="n">
-        <v>582.771258652471</v>
+        <v>5848.12551989594</v>
       </c>
       <c r="D20" t="s">
         <v>7</v>
@@ -699,10 +699,10 @@
         <v>6</v>
       </c>
       <c r="B21" s="1" t="n">
-        <v>45856</v>
+        <v>45835</v>
       </c>
       <c r="C21" t="n">
-        <v>3774.37460704209</v>
+        <v>795.27107195837</v>
       </c>
       <c r="D21" t="s">
         <v>7</v>
@@ -713,10 +713,10 @@
         <v>6</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>45863</v>
+        <v>45842</v>
       </c>
       <c r="C22" t="n">
-        <v>980.83008292323</v>
+        <v>2863.65866842687</v>
       </c>
       <c r="D22" t="s">
         <v>7</v>
@@ -727,10 +727,10 @@
         <v>6</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>45873</v>
+        <v>45849</v>
       </c>
       <c r="C23" t="n">
-        <v>3776.52151072127</v>
+        <v>582.771258652471</v>
       </c>
       <c r="D23" t="s">
         <v>7</v>
@@ -741,10 +741,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>45880</v>
+        <v>45856</v>
       </c>
       <c r="C24" t="n">
-        <v>4118.93954141025</v>
+        <v>3774.37460704209</v>
       </c>
       <c r="D24" t="s">
         <v>7</v>
@@ -755,10 +755,10 @@
         <v>6</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>45887</v>
+        <v>45863</v>
       </c>
       <c r="C25" t="n">
-        <v>3648.23270392578</v>
+        <v>980.83008292323</v>
       </c>
       <c r="D25" t="s">
         <v>7</v>
@@ -769,10 +769,10 @@
         <v>6</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>45894</v>
+        <v>45873</v>
       </c>
       <c r="C26" t="n">
-        <v>2828.4104784591</v>
+        <v>3776.52151072127</v>
       </c>
       <c r="D26" t="s">
         <v>7</v>
@@ -783,10 +783,10 @@
         <v>6</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>45901</v>
+        <v>45880</v>
       </c>
       <c r="C27" t="n">
-        <v>1609.55976707164</v>
+        <v>4118.93954141025</v>
       </c>
       <c r="D27" t="s">
         <v>7</v>
@@ -794,86 +794,86 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>45810</v>
+        <v>45887</v>
       </c>
       <c r="C28" t="n">
-        <v>1114.95841751639</v>
+        <v>3648.23270392578</v>
       </c>
       <c r="D28" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B29" s="1" t="n">
-        <v>45817</v>
+        <v>45894</v>
       </c>
       <c r="C29" t="n">
-        <v>3967.21046532345</v>
+        <v>2828.4104784591</v>
       </c>
       <c r="D29" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>45826</v>
+        <v>45901</v>
       </c>
       <c r="C30" t="n">
-        <v>3404.56710734529</v>
+        <v>1609.55976707164</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>45835</v>
+        <v>45908</v>
       </c>
       <c r="C31" t="n">
-        <v>1999.33410190424</v>
+        <v>863.703280702658</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>45842</v>
+        <v>45912</v>
       </c>
       <c r="C32" t="n">
-        <v>529.656630645944</v>
+        <v>4204.24412434881</v>
       </c>
       <c r="D32" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>45849</v>
+        <v>45918</v>
       </c>
       <c r="C33" t="n">
-        <v>4816.73679818835</v>
+        <v>56.8832320221224</v>
       </c>
       <c r="D33" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
@@ -881,10 +881,10 @@
         <v>8</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>45856</v>
+        <v>45810</v>
       </c>
       <c r="C34" t="n">
-        <v>2193.24328610956</v>
+        <v>1114.95841751639</v>
       </c>
       <c r="D34" t="s">
         <v>9</v>
@@ -895,10 +895,10 @@
         <v>8</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>45863</v>
+        <v>45817</v>
       </c>
       <c r="C35" t="n">
-        <v>3643.24026825053</v>
+        <v>3967.21046532345</v>
       </c>
       <c r="D35" t="s">
         <v>9</v>
@@ -909,10 +909,10 @@
         <v>8</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>45873</v>
+        <v>45826</v>
       </c>
       <c r="C36" t="n">
-        <v>3128.79369665423</v>
+        <v>3404.56710734529</v>
       </c>
       <c r="D36" t="s">
         <v>9</v>
@@ -923,10 +923,10 @@
         <v>8</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>45880</v>
+        <v>45835</v>
       </c>
       <c r="C37" t="n">
-        <v>4586.82933528355</v>
+        <v>1999.33410190424</v>
       </c>
       <c r="D37" t="s">
         <v>9</v>
@@ -937,10 +937,10 @@
         <v>8</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>45887</v>
+        <v>45842</v>
       </c>
       <c r="C38" t="n">
-        <v>3394.16343445068</v>
+        <v>529.656630645944</v>
       </c>
       <c r="D38" t="s">
         <v>9</v>
@@ -951,10 +951,10 @@
         <v>8</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>45894</v>
+        <v>45849</v>
       </c>
       <c r="C39" t="n">
-        <v>2703.9092133905</v>
+        <v>4816.73679818835</v>
       </c>
       <c r="D39" t="s">
         <v>9</v>
@@ -965,10 +965,10 @@
         <v>8</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>45901</v>
+        <v>45856</v>
       </c>
       <c r="C40" t="n">
-        <v>1785.31900434777</v>
+        <v>2193.24328610956</v>
       </c>
       <c r="D40" t="s">
         <v>9</v>
@@ -976,128 +976,128 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>45810</v>
+        <v>45863</v>
       </c>
       <c r="C41" t="n">
-        <v>896.001226735543</v>
+        <v>3643.24026825053</v>
       </c>
       <c r="D41" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>45817</v>
+        <v>45873</v>
       </c>
       <c r="C42" t="n">
-        <v>2030.70030492232</v>
+        <v>3128.79369665423</v>
       </c>
       <c r="D42" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>45826</v>
+        <v>45880</v>
       </c>
       <c r="C43" t="n">
-        <v>7084.27944063735</v>
+        <v>4586.82933528355</v>
       </c>
       <c r="D43" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>45835</v>
+        <v>45887</v>
       </c>
       <c r="C44" t="n">
-        <v>911.65002482044</v>
+        <v>3394.16343445068</v>
       </c>
       <c r="D44" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>45842</v>
+        <v>45894</v>
       </c>
       <c r="C45" t="n">
-        <v>923.42600524363</v>
+        <v>2703.9092133905</v>
       </c>
       <c r="D45" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B46" s="1" t="n">
-        <v>45849</v>
+        <v>45901</v>
       </c>
       <c r="C46" t="n">
-        <v>2298.37541327764</v>
+        <v>1785.31900434777</v>
       </c>
       <c r="D46" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>45856</v>
+        <v>45908</v>
       </c>
       <c r="C47" t="n">
-        <v>2548.92674654963</v>
+        <v>4661.49033559175</v>
       </c>
       <c r="D47" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>45863</v>
+        <v>45912</v>
       </c>
       <c r="C48" t="n">
-        <v>2284.96228575287</v>
+        <v>1775.28253834679</v>
       </c>
       <c r="D48" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>45873</v>
+        <v>45918</v>
       </c>
       <c r="C49" t="n">
-        <v>2405.49680671009</v>
+        <v>16.58013358516</v>
       </c>
       <c r="D49" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50">
@@ -1105,10 +1105,10 @@
         <v>10</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>45880</v>
+        <v>45810</v>
       </c>
       <c r="C50" t="n">
-        <v>5789.58956490831</v>
+        <v>896.001226735543</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
@@ -1119,10 +1119,10 @@
         <v>10</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>45887</v>
+        <v>45817</v>
       </c>
       <c r="C51" t="n">
-        <v>3313.54847929235</v>
+        <v>2030.70030492232</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
@@ -1133,10 +1133,10 @@
         <v>10</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>45894</v>
+        <v>45826</v>
       </c>
       <c r="C52" t="n">
-        <v>3187.1648559333</v>
+        <v>7084.27944063735</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
@@ -1147,10 +1147,10 @@
         <v>10</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>45901</v>
+        <v>45835</v>
       </c>
       <c r="C53" t="n">
-        <v>1469.24426484684</v>
+        <v>911.65002482044</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -1158,170 +1158,170 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>45810</v>
+        <v>45842</v>
       </c>
       <c r="C54" t="n">
-        <v>605.276401347038</v>
+        <v>923.42600524363</v>
       </c>
       <c r="D54" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>45817</v>
+        <v>45849</v>
       </c>
       <c r="C55" t="n">
-        <v>3254.15705318998</v>
+        <v>2298.37541327764</v>
       </c>
       <c r="D55" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B56" s="1" t="n">
-        <v>45826</v>
+        <v>45856</v>
       </c>
       <c r="C56" t="n">
-        <v>5494.93846571461</v>
+        <v>2548.92674654963</v>
       </c>
       <c r="D56" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>45835</v>
+        <v>45863</v>
       </c>
       <c r="C57" t="n">
-        <v>493.831746277201</v>
+        <v>2284.96228575287</v>
       </c>
       <c r="D57" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>45842</v>
+        <v>45873</v>
       </c>
       <c r="C58" t="n">
-        <v>1033.1066084577</v>
+        <v>2405.49680671009</v>
       </c>
       <c r="D58" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>45849</v>
+        <v>45880</v>
       </c>
       <c r="C59" t="n">
-        <v>809.578051527371</v>
+        <v>5789.58956490831</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>45856</v>
+        <v>45887</v>
       </c>
       <c r="C60" t="n">
-        <v>2699.12605710809</v>
+        <v>3313.54847929235</v>
       </c>
       <c r="D60" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>45863</v>
+        <v>45894</v>
       </c>
       <c r="C61" t="n">
-        <v>1219.60301108964</v>
+        <v>3187.1648559333</v>
       </c>
       <c r="D61" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>45873</v>
+        <v>45901</v>
       </c>
       <c r="C62" t="n">
-        <v>3429.90174797312</v>
+        <v>1469.24426484684</v>
       </c>
       <c r="D62" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>45880</v>
+        <v>45908</v>
       </c>
       <c r="C63" t="n">
-        <v>3447.29762872426</v>
+        <v>4410.13371410884</v>
       </c>
       <c r="D63" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>45887</v>
+        <v>45912</v>
       </c>
       <c r="C64" t="n">
-        <v>2971.31194167402</v>
+        <v>5088.9184064008</v>
       </c>
       <c r="D64" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>45894</v>
+        <v>45918</v>
       </c>
       <c r="C65" t="n">
-        <v>2128.81048195735</v>
+        <v>46.9554905447005</v>
       </c>
       <c r="D65" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -1329,10 +1329,10 @@
         <v>11</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>45901</v>
+        <v>45810</v>
       </c>
       <c r="C66" t="n">
-        <v>1885.52718940828</v>
+        <v>605.276401347038</v>
       </c>
       <c r="D66" t="s">
         <v>7</v>
@@ -1340,1105 +1340,1105 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>45810</v>
+        <v>45817</v>
       </c>
       <c r="C67" t="n">
-        <v>829.274264965441</v>
+        <v>3254.15705318998</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>45817</v>
+        <v>45826</v>
       </c>
       <c r="C68" t="n">
-        <v>2034.26328932924</v>
+        <v>5494.93846571461</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>45826</v>
+        <v>45835</v>
       </c>
       <c r="C69" t="n">
-        <v>3085.76309059706</v>
+        <v>493.831746277201</v>
       </c>
       <c r="D69" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>45835</v>
+        <v>45842</v>
       </c>
       <c r="C70" t="n">
-        <v>2113.86708643315</v>
+        <v>1033.1066084577</v>
       </c>
       <c r="D70" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>45842</v>
+        <v>45849</v>
       </c>
       <c r="C71" t="n">
-        <v>1158.7597584648</v>
+        <v>809.578051527371</v>
       </c>
       <c r="D71" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>45849</v>
+        <v>45856</v>
       </c>
       <c r="C72" t="n">
-        <v>3804.85995259262</v>
+        <v>2699.12605710809</v>
       </c>
       <c r="D72" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>45856</v>
+        <v>45863</v>
       </c>
       <c r="C73" t="n">
-        <v>1889.8067251411</v>
+        <v>1219.60301108964</v>
       </c>
       <c r="D73" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>45863</v>
+        <v>45873</v>
       </c>
       <c r="C74" t="n">
-        <v>4061.45488430826</v>
+        <v>3429.90174797312</v>
       </c>
       <c r="D74" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>45873</v>
+        <v>45880</v>
       </c>
       <c r="C75" t="n">
-        <v>2808.60882816944</v>
+        <v>3447.29762872426</v>
       </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>45880</v>
+        <v>45887</v>
       </c>
       <c r="C76" t="n">
-        <v>4334.8959831226</v>
+        <v>2971.31194167402</v>
       </c>
       <c r="D76" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>45887</v>
+        <v>45894</v>
       </c>
       <c r="C77" t="n">
-        <v>1799.96285583044</v>
+        <v>2128.81048195735</v>
       </c>
       <c r="D77" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" s="1" t="n">
-        <v>45894</v>
+        <v>45901</v>
       </c>
       <c r="C78" t="n">
-        <v>3245.54806926349</v>
+        <v>1885.52718940828</v>
       </c>
       <c r="D78" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>45901</v>
+        <v>45908</v>
       </c>
       <c r="C79" t="n">
-        <v>1181.54431177802</v>
+        <v>955.895358696291</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>45810</v>
+        <v>45912</v>
       </c>
       <c r="C80" t="n">
-        <v>926.247921016511</v>
+        <v>4439.99904036154</v>
       </c>
       <c r="D80" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>45817</v>
+        <v>45918</v>
       </c>
       <c r="C81" t="n">
-        <v>1013.90634494399</v>
+        <v>39.7251409513983</v>
       </c>
       <c r="D81" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>45826</v>
+        <v>45810</v>
       </c>
       <c r="C82" t="n">
-        <v>2492.6382352641</v>
+        <v>829.274264965441</v>
       </c>
       <c r="D82" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>45835</v>
+        <v>45817</v>
       </c>
       <c r="C83" t="n">
-        <v>208.353459554264</v>
+        <v>2034.26328932924</v>
       </c>
       <c r="D83" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>45842</v>
+        <v>45826</v>
       </c>
       <c r="C84" t="n">
-        <v>642.842381753608</v>
+        <v>3085.76309059706</v>
       </c>
       <c r="D84" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B85" s="1" t="n">
-        <v>45849</v>
+        <v>45835</v>
       </c>
       <c r="C85" t="n">
-        <v>708.264946681898</v>
+        <v>2113.86708643315</v>
       </c>
       <c r="D85" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>45856</v>
+        <v>45842</v>
       </c>
       <c r="C86" t="n">
-        <v>1297.74874736552</v>
+        <v>1158.7597584648</v>
       </c>
       <c r="D86" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>45863</v>
+        <v>45849</v>
       </c>
       <c r="C87" t="n">
-        <v>1282.98566492001</v>
+        <v>3804.85995259262</v>
       </c>
       <c r="D87" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>45873</v>
+        <v>45856</v>
       </c>
       <c r="C88" t="n">
-        <v>3039.25791166093</v>
+        <v>1889.8067251411</v>
       </c>
       <c r="D88" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>45880</v>
+        <v>45863</v>
       </c>
       <c r="C89" t="n">
-        <v>4775.20972744648</v>
+        <v>4061.45488430826</v>
       </c>
       <c r="D89" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>45887</v>
+        <v>45873</v>
       </c>
       <c r="C90" t="n">
-        <v>2089.81926332235</v>
+        <v>2808.60882816944</v>
       </c>
       <c r="D90" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>45894</v>
+        <v>45880</v>
       </c>
       <c r="C91" t="n">
-        <v>4752.47660961459</v>
+        <v>4334.8959831226</v>
       </c>
       <c r="D91" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>45901</v>
+        <v>45887</v>
       </c>
       <c r="C92" t="n">
-        <v>1541.24223720587</v>
+        <v>1799.96285583044</v>
       </c>
       <c r="D92" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>45810</v>
+        <v>45894</v>
       </c>
       <c r="C93" t="n">
-        <v>820.429289044661</v>
+        <v>3245.54806926349</v>
       </c>
       <c r="D93" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>45817</v>
+        <v>45901</v>
       </c>
       <c r="C94" t="n">
-        <v>4438.5887346754</v>
+        <v>1181.54431177802</v>
       </c>
       <c r="D94" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B95" s="1" t="n">
-        <v>45826</v>
+        <v>45908</v>
       </c>
       <c r="C95" t="n">
-        <v>3375.80821888685</v>
+        <v>1565.61592820745</v>
       </c>
       <c r="D95" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B96" s="1" t="n">
-        <v>45835</v>
+        <v>45912</v>
       </c>
       <c r="C96" t="n">
-        <v>783.186507035906</v>
+        <v>1461.3157191967</v>
       </c>
       <c r="D96" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>45842</v>
+        <v>45918</v>
       </c>
       <c r="C97" t="n">
-        <v>631.923814275014</v>
+        <v>31.2360864618781</v>
       </c>
       <c r="D97" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>45849</v>
+        <v>45810</v>
       </c>
       <c r="C98" t="n">
-        <v>1315.52124698387</v>
+        <v>926.247921016511</v>
       </c>
       <c r="D98" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>45856</v>
+        <v>45817</v>
       </c>
       <c r="C99" t="n">
-        <v>2207.89437180403</v>
+        <v>1013.90634494399</v>
       </c>
       <c r="D99" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>45863</v>
+        <v>45826</v>
       </c>
       <c r="C100" t="n">
-        <v>2258.29619366983</v>
+        <v>2492.6382352641</v>
       </c>
       <c r="D100" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>45873</v>
+        <v>45835</v>
       </c>
       <c r="C101" t="n">
-        <v>3728.99958287456</v>
+        <v>208.353459554264</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>45880</v>
+        <v>45842</v>
       </c>
       <c r="C102" t="n">
-        <v>3912.32265691079</v>
+        <v>642.842381753608</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>45887</v>
+        <v>45849</v>
       </c>
       <c r="C103" t="n">
-        <v>3599.81922977165</v>
+        <v>708.264946681898</v>
       </c>
       <c r="D103" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>45894</v>
+        <v>45856</v>
       </c>
       <c r="C104" t="n">
-        <v>2913.7632567457</v>
+        <v>1297.74874736552</v>
       </c>
       <c r="D104" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>45901</v>
+        <v>45863</v>
       </c>
       <c r="C105" t="n">
-        <v>2488.12022404981</v>
+        <v>1282.98566492001</v>
       </c>
       <c r="D105" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>45810</v>
+        <v>45873</v>
       </c>
       <c r="C106" t="n">
-        <v>749.87306919933</v>
+        <v>3039.25791166093</v>
       </c>
       <c r="D106" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B107" s="1" t="n">
-        <v>45817</v>
+        <v>45880</v>
       </c>
       <c r="C107" t="n">
-        <v>4412.64180269369</v>
+        <v>4775.20972744648</v>
       </c>
       <c r="D107" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>45826</v>
+        <v>45887</v>
       </c>
       <c r="C108" t="n">
-        <v>6968.33616394737</v>
+        <v>2089.81926332235</v>
       </c>
       <c r="D108" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>45835</v>
+        <v>45894</v>
       </c>
       <c r="C109" t="n">
-        <v>1687.73157419569</v>
+        <v>4752.47660961459</v>
       </c>
       <c r="D109" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B110" s="1" t="n">
-        <v>45842</v>
+        <v>45901</v>
       </c>
       <c r="C110" t="n">
-        <v>761.833024239517</v>
+        <v>1541.24223720587</v>
       </c>
       <c r="D110" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>45849</v>
+        <v>45908</v>
       </c>
       <c r="C111" t="n">
-        <v>2588.80886828618</v>
+        <v>1063.45963611384</v>
       </c>
       <c r="D111" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>45856</v>
+        <v>45912</v>
       </c>
       <c r="C112" t="n">
-        <v>3605.2695200209</v>
+        <v>940.00173894257</v>
       </c>
       <c r="D112" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>45863</v>
+        <v>45918</v>
       </c>
       <c r="C113" t="n">
-        <v>2464.37485564112</v>
+        <v>31.3335119250464</v>
       </c>
       <c r="D113" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>45873</v>
+        <v>45810</v>
       </c>
       <c r="C114" t="n">
-        <v>3566.94051479447</v>
+        <v>820.429289044661</v>
       </c>
       <c r="D114" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>45880</v>
+        <v>45817</v>
       </c>
       <c r="C115" t="n">
-        <v>5545.11780891709</v>
+        <v>4438.5887346754</v>
       </c>
       <c r="D115" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>45887</v>
+        <v>45826</v>
       </c>
       <c r="C116" t="n">
-        <v>2723.46038359217</v>
+        <v>3375.80821888685</v>
       </c>
       <c r="D116" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>45894</v>
+        <v>45835</v>
       </c>
       <c r="C117" t="n">
-        <v>3638.2311832252</v>
+        <v>783.186507035906</v>
       </c>
       <c r="D117" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>45901</v>
+        <v>45842</v>
       </c>
       <c r="C118" t="n">
-        <v>1849.60594842151</v>
+        <v>631.923814275014</v>
       </c>
       <c r="D118" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B119" s="1" t="n">
-        <v>45810</v>
+        <v>45849</v>
       </c>
       <c r="C119" t="n">
-        <v>654.622171815671</v>
+        <v>1315.52124698387</v>
       </c>
       <c r="D119" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>45817</v>
+        <v>45856</v>
       </c>
       <c r="C120" t="n">
-        <v>836.306701729539</v>
+        <v>2207.89437180403</v>
       </c>
       <c r="D120" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B121" s="1" t="n">
-        <v>45826</v>
+        <v>45863</v>
       </c>
       <c r="C121" t="n">
-        <v>752.809303565924</v>
+        <v>2258.29619366983</v>
       </c>
       <c r="D121" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>45835</v>
+        <v>45873</v>
       </c>
       <c r="C122" t="n">
-        <v>361.937925301449</v>
+        <v>3728.99958287456</v>
       </c>
       <c r="D122" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>45842</v>
+        <v>45880</v>
       </c>
       <c r="C123" t="n">
-        <v>274.147297459927</v>
+        <v>3912.32265691079</v>
       </c>
       <c r="D123" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>45849</v>
+        <v>45887</v>
       </c>
       <c r="C124" t="n">
-        <v>638.156969539091</v>
+        <v>3599.81922977165</v>
       </c>
       <c r="D124" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>45856</v>
+        <v>45894</v>
       </c>
       <c r="C125" t="n">
-        <v>671.100601945576</v>
+        <v>2913.7632567457</v>
       </c>
       <c r="D125" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>45863</v>
+        <v>45901</v>
       </c>
       <c r="C126" t="n">
-        <v>1126.92089194702</v>
+        <v>2488.12022404981</v>
       </c>
       <c r="D126" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>45873</v>
+        <v>45908</v>
       </c>
       <c r="C127" t="n">
-        <v>1904.69958425363</v>
+        <v>1047.56782225816</v>
       </c>
       <c r="D127" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B128" s="1" t="n">
-        <v>45880</v>
+        <v>45912</v>
       </c>
       <c r="C128" t="n">
-        <v>3800.93540490905</v>
+        <v>1336.84030216341</v>
       </c>
       <c r="D128" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>45887</v>
+        <v>45918</v>
       </c>
       <c r="C129" t="n">
-        <v>2170.9732688459</v>
+        <v>106.835647202663</v>
       </c>
       <c r="D129" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>45894</v>
+        <v>45810</v>
       </c>
       <c r="C130" t="n">
-        <v>3307.44136835169</v>
+        <v>749.87306919933</v>
       </c>
       <c r="D130" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>45901</v>
+        <v>45817</v>
       </c>
       <c r="C131" t="n">
-        <v>988.497215490608</v>
+        <v>4412.64180269369</v>
       </c>
       <c r="D131" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>45810</v>
+        <v>45826</v>
       </c>
       <c r="C132" t="n">
-        <v>714.089199892923</v>
+        <v>6968.33616394737</v>
       </c>
       <c r="D132" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>45817</v>
+        <v>45835</v>
       </c>
       <c r="C133" t="n">
-        <v>1332.31394460659</v>
+        <v>1687.73157419569</v>
       </c>
       <c r="D133" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>45826</v>
+        <v>45842</v>
       </c>
       <c r="C134" t="n">
-        <v>1403.48926864965</v>
+        <v>761.833024239517</v>
       </c>
       <c r="D134" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>45835</v>
+        <v>45849</v>
       </c>
       <c r="C135" t="n">
-        <v>423.584800449672</v>
+        <v>2588.80886828618</v>
       </c>
       <c r="D135" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>45842</v>
+        <v>45856</v>
       </c>
       <c r="C136" t="n">
-        <v>691.944631498715</v>
+        <v>3605.2695200209</v>
       </c>
       <c r="D136" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>45849</v>
+        <v>45863</v>
       </c>
       <c r="C137" t="n">
-        <v>1520.16740554049</v>
+        <v>2464.37485564112</v>
       </c>
       <c r="D137" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>45856</v>
+        <v>45873</v>
       </c>
       <c r="C138" t="n">
-        <v>1394.70386978331</v>
+        <v>3566.94051479447</v>
       </c>
       <c r="D138" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B139" s="1" t="n">
-        <v>45863</v>
+        <v>45880</v>
       </c>
       <c r="C139" t="n">
-        <v>1945.74582627245</v>
+        <v>5545.11780891709</v>
       </c>
       <c r="D139" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>45873</v>
+        <v>45887</v>
       </c>
       <c r="C140" t="n">
-        <v>2541.97761269932</v>
+        <v>2723.46038359217</v>
       </c>
       <c r="D140" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>45880</v>
+        <v>45894</v>
       </c>
       <c r="C141" t="n">
-        <v>3884.74955947511</v>
+        <v>3638.2311832252</v>
       </c>
       <c r="D141" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B142" s="1" t="n">
-        <v>45887</v>
+        <v>45901</v>
       </c>
       <c r="C142" t="n">
-        <v>1740.78269526192</v>
+        <v>1849.60594842151</v>
       </c>
       <c r="D142" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>45894</v>
+        <v>45908</v>
       </c>
       <c r="C143" t="n">
-        <v>2505.19645489012</v>
+        <v>2404.95349211011</v>
       </c>
       <c r="D143" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B144" s="1" t="n">
-        <v>45901</v>
+        <v>45912</v>
       </c>
       <c r="C144" t="n">
-        <v>973.643220252498</v>
+        <v>2923.99496976121</v>
       </c>
       <c r="D144" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B145" s="1" t="n">
-        <v>45810</v>
+        <v>45918</v>
       </c>
       <c r="C145" t="n">
-        <v>397.290437761417</v>
+        <v>30.5264686545068</v>
       </c>
       <c r="D145" t="s">
         <v>9</v>
@@ -2446,181 +2446,181 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>45817</v>
+        <v>45810</v>
       </c>
       <c r="C146" t="n">
-        <v>1926.90668700788</v>
+        <v>654.622171815671</v>
       </c>
       <c r="D146" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>45826</v>
+        <v>45817</v>
       </c>
       <c r="C147" t="n">
-        <v>3021.29841712424</v>
+        <v>836.306701729539</v>
       </c>
       <c r="D147" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>45835</v>
+        <v>45826</v>
       </c>
       <c r="C148" t="n">
-        <v>957.104912247124</v>
+        <v>752.809303565924</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>45842</v>
+        <v>45835</v>
       </c>
       <c r="C149" t="n">
-        <v>1649.6084629323</v>
+        <v>361.937925301449</v>
       </c>
       <c r="D149" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>45849</v>
+        <v>45842</v>
       </c>
       <c r="C150" t="n">
-        <v>1539.67899281552</v>
+        <v>274.147297459927</v>
       </c>
       <c r="D150" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>45856</v>
+        <v>45849</v>
       </c>
       <c r="C151" t="n">
-        <v>2459.63795093809</v>
+        <v>638.156969539091</v>
       </c>
       <c r="D151" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B152" s="1" t="n">
-        <v>45863</v>
+        <v>45856</v>
       </c>
       <c r="C152" t="n">
-        <v>1996.741477782</v>
+        <v>671.100601945576</v>
       </c>
       <c r="D152" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>45873</v>
+        <v>45863</v>
       </c>
       <c r="C153" t="n">
-        <v>3847.37405848995</v>
+        <v>1126.92089194702</v>
       </c>
       <c r="D153" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B154" s="1" t="n">
-        <v>45880</v>
+        <v>45873</v>
       </c>
       <c r="C154" t="n">
-        <v>2828.98818979552</v>
+        <v>1904.69958425363</v>
       </c>
       <c r="D154" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>45887</v>
+        <v>45880</v>
       </c>
       <c r="C155" t="n">
-        <v>2591.30540522796</v>
+        <v>3800.93540490905</v>
       </c>
       <c r="D155" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>45894</v>
+        <v>45887</v>
       </c>
       <c r="C156" t="n">
-        <v>1495.1664275966</v>
+        <v>2170.9732688459</v>
       </c>
       <c r="D156" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>45901</v>
+        <v>45894</v>
       </c>
       <c r="C157" t="n">
-        <v>1208.07345867435</v>
+        <v>3307.44136835169</v>
       </c>
       <c r="D157" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>45810</v>
+        <v>45901</v>
       </c>
       <c r="C158" t="n">
-        <v>564.435194569703</v>
+        <v>988.497215490608</v>
       </c>
       <c r="D158" t="s">
         <v>5</v>
@@ -2628,13 +2628,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>45817</v>
+        <v>45908</v>
       </c>
       <c r="C159" t="n">
-        <v>1545.70814869222</v>
+        <v>1157.73106587574</v>
       </c>
       <c r="D159" t="s">
         <v>5</v>
@@ -2642,13 +2642,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>45826</v>
+        <v>45912</v>
       </c>
       <c r="C160" t="n">
-        <v>3858.60188057439</v>
+        <v>898.830115935534</v>
       </c>
       <c r="D160" t="s">
         <v>5</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>45835</v>
+        <v>45918</v>
       </c>
       <c r="C161" t="n">
-        <v>75.8890033270052</v>
+        <v>10.4976730559286</v>
       </c>
       <c r="D161" t="s">
         <v>5</v>
@@ -2670,139 +2670,139 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>45842</v>
+        <v>45810</v>
       </c>
       <c r="C162" t="n">
-        <v>1607.81816898261</v>
+        <v>714.089199892923</v>
       </c>
       <c r="D162" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>45849</v>
+        <v>45817</v>
       </c>
       <c r="C163" t="n">
-        <v>651.305214716471</v>
+        <v>1332.31394460659</v>
       </c>
       <c r="D163" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B164" s="1" t="n">
-        <v>45856</v>
+        <v>45826</v>
       </c>
       <c r="C164" t="n">
-        <v>3182.90047392644</v>
+        <v>1403.48926864965</v>
       </c>
       <c r="D164" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B165" s="1" t="n">
-        <v>45863</v>
+        <v>45835</v>
       </c>
       <c r="C165" t="n">
-        <v>1054.40680471126</v>
+        <v>423.584800449672</v>
       </c>
       <c r="D165" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B166" s="1" t="n">
-        <v>45873</v>
+        <v>45842</v>
       </c>
       <c r="C166" t="n">
-        <v>3589.214407389</v>
+        <v>691.944631498715</v>
       </c>
       <c r="D166" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B167" s="1" t="n">
-        <v>45880</v>
+        <v>45849</v>
       </c>
       <c r="C167" t="n">
-        <v>2375.18299388371</v>
+        <v>1520.16740554049</v>
       </c>
       <c r="D167" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B168" s="1" t="n">
-        <v>45887</v>
+        <v>45856</v>
       </c>
       <c r="C168" t="n">
-        <v>2768.14096770644</v>
+        <v>1394.70386978331</v>
       </c>
       <c r="D168" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B169" s="1" t="n">
-        <v>45894</v>
+        <v>45863</v>
       </c>
       <c r="C169" t="n">
-        <v>1810.23398806605</v>
+        <v>1945.74582627245</v>
       </c>
       <c r="D169" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B170" s="1" t="n">
-        <v>45901</v>
+        <v>45873</v>
       </c>
       <c r="C170" t="n">
-        <v>2132.26773713034</v>
+        <v>2541.97761269932</v>
       </c>
       <c r="D170" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B171" s="1" t="n">
-        <v>45810</v>
+        <v>45880</v>
       </c>
       <c r="C171" t="n">
-        <v>447.392417911663</v>
+        <v>3884.74955947511</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
@@ -2810,13 +2810,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B172" s="1" t="n">
-        <v>45817</v>
+        <v>45887</v>
       </c>
       <c r="C172" t="n">
-        <v>2644.87800920049</v>
+        <v>1740.78269526192</v>
       </c>
       <c r="D172" t="s">
         <v>7</v>
@@ -2824,13 +2824,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B173" s="1" t="n">
-        <v>45826</v>
+        <v>45894</v>
       </c>
       <c r="C173" t="n">
-        <v>2858.8009710539</v>
+        <v>2505.19645489012</v>
       </c>
       <c r="D173" t="s">
         <v>7</v>
@@ -2838,13 +2838,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B174" s="1" t="n">
-        <v>45835</v>
+        <v>45901</v>
       </c>
       <c r="C174" t="n">
-        <v>763.112592784348</v>
+        <v>973.643220252498</v>
       </c>
       <c r="D174" t="s">
         <v>7</v>
@@ -2852,13 +2852,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B175" s="1" t="n">
-        <v>45842</v>
+        <v>45908</v>
       </c>
       <c r="C175" t="n">
-        <v>674.542028148127</v>
+        <v>929.750735529288</v>
       </c>
       <c r="D175" t="s">
         <v>7</v>
@@ -2866,13 +2866,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>45849</v>
+        <v>45912</v>
       </c>
       <c r="C176" t="n">
-        <v>1744.34596755931</v>
+        <v>863.428526988611</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>45856</v>
+        <v>45918</v>
       </c>
       <c r="C177" t="n">
-        <v>1143.7372540643</v>
+        <v>31.4349107910936</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -2894,97 +2894,97 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B178" s="1" t="n">
-        <v>45863</v>
+        <v>45810</v>
       </c>
       <c r="C178" t="n">
-        <v>2601.30753317707</v>
+        <v>397.290437761417</v>
       </c>
       <c r="D178" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B179" s="1" t="n">
-        <v>45873</v>
+        <v>45817</v>
       </c>
       <c r="C179" t="n">
-        <v>2436.60825019887</v>
+        <v>1926.90668700788</v>
       </c>
       <c r="D179" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B180" s="1" t="n">
-        <v>45880</v>
+        <v>45826</v>
       </c>
       <c r="C180" t="n">
-        <v>3629.61304883485</v>
+        <v>3021.29841712424</v>
       </c>
       <c r="D180" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B181" s="1" t="n">
-        <v>45887</v>
+        <v>45835</v>
       </c>
       <c r="C181" t="n">
-        <v>2475.83592992463</v>
+        <v>957.104912247124</v>
       </c>
       <c r="D181" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>45894</v>
+        <v>45842</v>
       </c>
       <c r="C182" t="n">
-        <v>2279.65892583665</v>
+        <v>1649.6084629323</v>
       </c>
       <c r="D182" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B183" s="1" t="n">
-        <v>45901</v>
+        <v>45849</v>
       </c>
       <c r="C183" t="n">
-        <v>998.259977017587</v>
+        <v>1539.67899281552</v>
       </c>
       <c r="D183" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B184" s="1" t="n">
-        <v>45810</v>
+        <v>45856</v>
       </c>
       <c r="C184" t="n">
-        <v>844.462537825576</v>
+        <v>2459.63795093809</v>
       </c>
       <c r="D184" t="s">
         <v>9</v>
@@ -2992,13 +2992,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>45817</v>
+        <v>45863</v>
       </c>
       <c r="C185" t="n">
-        <v>2607.51843632838</v>
+        <v>1996.741477782</v>
       </c>
       <c r="D185" t="s">
         <v>9</v>
@@ -3006,13 +3006,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B186" s="1" t="n">
-        <v>45826</v>
+        <v>45873</v>
       </c>
       <c r="C186" t="n">
-        <v>1205.84904980573</v>
+        <v>3847.37405848995</v>
       </c>
       <c r="D186" t="s">
         <v>9</v>
@@ -3020,13 +3020,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B187" s="1" t="n">
-        <v>45835</v>
+        <v>45880</v>
       </c>
       <c r="C187" t="n">
-        <v>394.51261524864</v>
+        <v>2828.98818979552</v>
       </c>
       <c r="D187" t="s">
         <v>9</v>
@@ -3034,13 +3034,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>45842</v>
+        <v>45887</v>
       </c>
       <c r="C188" t="n">
-        <v>296.790183728622</v>
+        <v>2591.30540522796</v>
       </c>
       <c r="D188" t="s">
         <v>9</v>
@@ -3048,13 +3048,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B189" s="1" t="n">
-        <v>45849</v>
+        <v>45894</v>
       </c>
       <c r="C189" t="n">
-        <v>1029.40856752812</v>
+        <v>1495.1664275966</v>
       </c>
       <c r="D189" t="s">
         <v>9</v>
@@ -3062,13 +3062,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>45856</v>
+        <v>45901</v>
       </c>
       <c r="C190" t="n">
-        <v>822.899413189293</v>
+        <v>1208.07345867435</v>
       </c>
       <c r="D190" t="s">
         <v>9</v>
@@ -3076,13 +3076,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B191" s="1" t="n">
-        <v>45863</v>
+        <v>45908</v>
       </c>
       <c r="C191" t="n">
-        <v>1093.38451398619</v>
+        <v>1178.95542275766</v>
       </c>
       <c r="D191" t="s">
         <v>9</v>
@@ -3090,13 +3090,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B192" s="1" t="n">
-        <v>45873</v>
+        <v>45912</v>
       </c>
       <c r="C192" t="n">
-        <v>2628.07482556948</v>
+        <v>673.255967264892</v>
       </c>
       <c r="D192" t="s">
         <v>9</v>
@@ -3104,13 +3104,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>45880</v>
+        <v>45918</v>
       </c>
       <c r="C193" t="n">
-        <v>2995.86132481368</v>
+        <v>39.4795373586977</v>
       </c>
       <c r="D193" t="s">
         <v>9</v>
@@ -3118,43 +3118,673 @@
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B194" s="1" t="n">
-        <v>45887</v>
+        <v>45810</v>
       </c>
       <c r="C194" t="n">
-        <v>2000.21497594218</v>
+        <v>564.435194569703</v>
       </c>
       <c r="D194" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B195" s="1" t="n">
-        <v>45894</v>
+        <v>45817</v>
       </c>
       <c r="C195" t="n">
-        <v>1879.36457990422</v>
+        <v>1545.70814869222</v>
       </c>
       <c r="D195" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
+        <v>19</v>
+      </c>
+      <c r="B196" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C196" t="n">
+        <v>3858.60188057439</v>
+      </c>
+      <c r="D196" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>19</v>
+      </c>
+      <c r="B197" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C197" t="n">
+        <v>75.8890033270052</v>
+      </c>
+      <c r="D197" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>19</v>
+      </c>
+      <c r="B198" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C198" t="n">
+        <v>1607.81816898261</v>
+      </c>
+      <c r="D198" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>19</v>
+      </c>
+      <c r="B199" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C199" t="n">
+        <v>651.305214716471</v>
+      </c>
+      <c r="D199" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>19</v>
+      </c>
+      <c r="B200" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C200" t="n">
+        <v>3182.90047392644</v>
+      </c>
+      <c r="D200" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>19</v>
+      </c>
+      <c r="B201" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C201" t="n">
+        <v>1054.40680471126</v>
+      </c>
+      <c r="D201" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>19</v>
+      </c>
+      <c r="B202" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C202" t="n">
+        <v>3589.214407389</v>
+      </c>
+      <c r="D202" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>19</v>
+      </c>
+      <c r="B203" s="1" t="n">
+        <v>45880</v>
+      </c>
+      <c r="C203" t="n">
+        <v>2375.18299388371</v>
+      </c>
+      <c r="D203" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>19</v>
+      </c>
+      <c r="B204" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="C204" t="n">
+        <v>2768.14096770644</v>
+      </c>
+      <c r="D204" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>19</v>
+      </c>
+      <c r="B205" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="C205" t="n">
+        <v>1810.23398806605</v>
+      </c>
+      <c r="D205" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>19</v>
+      </c>
+      <c r="B206" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C206" t="n">
+        <v>2132.26773713034</v>
+      </c>
+      <c r="D206" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>19</v>
+      </c>
+      <c r="B207" s="1" t="n">
+        <v>45908</v>
+      </c>
+      <c r="C207" t="n">
+        <v>604.718699330132</v>
+      </c>
+      <c r="D207" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>19</v>
+      </c>
+      <c r="B208" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="C208" t="n">
+        <v>435.877350957814</v>
+      </c>
+      <c r="D208" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>19</v>
+      </c>
+      <c r="B209" s="1" t="n">
+        <v>45918</v>
+      </c>
+      <c r="C209" t="n">
+        <v>55.6387261658514</v>
+      </c>
+      <c r="D209" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>20</v>
+      </c>
+      <c r="B210" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C210" t="n">
+        <v>447.392417911663</v>
+      </c>
+      <c r="D210" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>20</v>
+      </c>
+      <c r="B211" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C211" t="n">
+        <v>2644.87800920049</v>
+      </c>
+      <c r="D211" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>20</v>
+      </c>
+      <c r="B212" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C212" t="n">
+        <v>2858.8009710539</v>
+      </c>
+      <c r="D212" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>20</v>
+      </c>
+      <c r="B213" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C213" t="n">
+        <v>763.112592784348</v>
+      </c>
+      <c r="D213" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>20</v>
+      </c>
+      <c r="B214" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C214" t="n">
+        <v>674.542028148127</v>
+      </c>
+      <c r="D214" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>20</v>
+      </c>
+      <c r="B215" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C215" t="n">
+        <v>1744.34596755931</v>
+      </c>
+      <c r="D215" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>20</v>
+      </c>
+      <c r="B216" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C216" t="n">
+        <v>1143.7372540643</v>
+      </c>
+      <c r="D216" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>20</v>
+      </c>
+      <c r="B217" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C217" t="n">
+        <v>2601.30753317707</v>
+      </c>
+      <c r="D217" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>20</v>
+      </c>
+      <c r="B218" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C218" t="n">
+        <v>2436.60825019887</v>
+      </c>
+      <c r="D218" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>20</v>
+      </c>
+      <c r="B219" s="1" t="n">
+        <v>45880</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3629.61304883485</v>
+      </c>
+      <c r="D219" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>20</v>
+      </c>
+      <c r="B220" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="C220" t="n">
+        <v>2475.83592992463</v>
+      </c>
+      <c r="D220" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>20</v>
+      </c>
+      <c r="B221" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="C221" t="n">
+        <v>2279.65892583665</v>
+      </c>
+      <c r="D221" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>20</v>
+      </c>
+      <c r="B222" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="C222" t="n">
+        <v>998.259977017587</v>
+      </c>
+      <c r="D222" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>20</v>
+      </c>
+      <c r="B223" s="1" t="n">
+        <v>45908</v>
+      </c>
+      <c r="C223" t="n">
+        <v>867.84005325841</v>
+      </c>
+      <c r="D223" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>20</v>
+      </c>
+      <c r="B224" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1313.90964847212</v>
+      </c>
+      <c r="D224" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>20</v>
+      </c>
+      <c r="B225" s="1" t="n">
+        <v>45918</v>
+      </c>
+      <c r="C225" t="n">
+        <v>30.7415294568651</v>
+      </c>
+      <c r="D225" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
         <v>21</v>
       </c>
-      <c r="B196" s="1" t="n">
+      <c r="B226" s="1" t="n">
+        <v>45810</v>
+      </c>
+      <c r="C226" t="n">
+        <v>844.462537825576</v>
+      </c>
+      <c r="D226" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>21</v>
+      </c>
+      <c r="B227" s="1" t="n">
+        <v>45817</v>
+      </c>
+      <c r="C227" t="n">
+        <v>2607.51843632838</v>
+      </c>
+      <c r="D227" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>21</v>
+      </c>
+      <c r="B228" s="1" t="n">
+        <v>45826</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1205.84904980573</v>
+      </c>
+      <c r="D228" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>21</v>
+      </c>
+      <c r="B229" s="1" t="n">
+        <v>45835</v>
+      </c>
+      <c r="C229" t="n">
+        <v>394.51261524864</v>
+      </c>
+      <c r="D229" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>21</v>
+      </c>
+      <c r="B230" s="1" t="n">
+        <v>45842</v>
+      </c>
+      <c r="C230" t="n">
+        <v>296.790183728622</v>
+      </c>
+      <c r="D230" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>21</v>
+      </c>
+      <c r="B231" s="1" t="n">
+        <v>45849</v>
+      </c>
+      <c r="C231" t="n">
+        <v>1029.40856752812</v>
+      </c>
+      <c r="D231" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>21</v>
+      </c>
+      <c r="B232" s="1" t="n">
+        <v>45856</v>
+      </c>
+      <c r="C232" t="n">
+        <v>822.899413189293</v>
+      </c>
+      <c r="D232" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>21</v>
+      </c>
+      <c r="B233" s="1" t="n">
+        <v>45863</v>
+      </c>
+      <c r="C233" t="n">
+        <v>1093.38451398619</v>
+      </c>
+      <c r="D233" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>21</v>
+      </c>
+      <c r="B234" s="1" t="n">
+        <v>45873</v>
+      </c>
+      <c r="C234" t="n">
+        <v>2628.07482556948</v>
+      </c>
+      <c r="D234" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>21</v>
+      </c>
+      <c r="B235" s="1" t="n">
+        <v>45880</v>
+      </c>
+      <c r="C235" t="n">
+        <v>2995.86132481368</v>
+      </c>
+      <c r="D235" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>21</v>
+      </c>
+      <c r="B236" s="1" t="n">
+        <v>45887</v>
+      </c>
+      <c r="C236" t="n">
+        <v>2000.21497594218</v>
+      </c>
+      <c r="D236" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>21</v>
+      </c>
+      <c r="B237" s="1" t="n">
+        <v>45894</v>
+      </c>
+      <c r="C237" t="n">
+        <v>1879.36457990422</v>
+      </c>
+      <c r="D237" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>21</v>
+      </c>
+      <c r="B238" s="1" t="n">
         <v>45901</v>
       </c>
-      <c r="C196" t="n">
+      <c r="C238" t="n">
         <v>967.384492520583</v>
       </c>
-      <c r="D196" t="s">
+      <c r="D238" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>21</v>
+      </c>
+      <c r="B239" s="1" t="n">
+        <v>45908</v>
+      </c>
+      <c r="C239" t="n">
+        <v>497.796936645038</v>
+      </c>
+      <c r="D239" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>21</v>
+      </c>
+      <c r="B240" s="1" t="n">
+        <v>45912</v>
+      </c>
+      <c r="C240" t="n">
+        <v>542.217662983649</v>
+      </c>
+      <c r="D240" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>21</v>
+      </c>
+      <c r="B241" s="1" t="n">
+        <v>45918</v>
+      </c>
+      <c r="C241" t="n">
+        <v>39.5592660515528</v>
+      </c>
+      <c r="D241" t="s">
         <v>9</v>
       </c>
     </row>
